--- a/data/courses2026.xlsx
+++ b/data/courses2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e13bdd535dbd58c2/Documents/SMANA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\sma-site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D6FC58D-C18D-4813-94B9-74FD5048EF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481BE090-B0CB-4FCC-A51A-1B1763717673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="20700" windowHeight="12300" xr2:uid="{8748630B-DFF4-463D-818E-93A8B0D5FCB5}"/>
+    <workbookView xWindow="5205" yWindow="1215" windowWidth="17970" windowHeight="13470" activeTab="4" xr2:uid="{8748630B-DFF4-463D-818E-93A8B0D5FCB5}"/>
   </bookViews>
   <sheets>
     <sheet name="MARS 26" sheetId="2" r:id="rId1"/>
@@ -269,7 +269,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="131">
   <si>
     <t>TITULAIRES</t>
   </si>
@@ -380,9 +380,6 @@
   </si>
   <si>
     <t>10 KM DE SAINT MEDARD</t>
-  </si>
-  <si>
-    <t>18 juillrt</t>
   </si>
   <si>
     <t>BRIE</t>
@@ -2228,6 +2225,86 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -2240,15 +2317,35 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2264,105 +2361,26 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2391,46 +2409,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2748,29 +2745,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A5C4B4-F26D-4F2E-827B-7FDC23D66B44}">
   <dimension ref="A1:T55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" style="66" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="68" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="68" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="212" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="68" customWidth="1"/>
-    <col min="6" max="6" width="17.7265625" style="68" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="116" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" style="68" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" style="68" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="68" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" style="68" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" style="68" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="68"/>
-    <col min="14" max="14" width="11.7265625" style="170" customWidth="1"/>
-    <col min="15" max="15" width="12.26953125" style="170" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="68" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="68" customWidth="1"/>
-    <col min="18" max="16384" width="11.453125" style="66"/>
+    <col min="1" max="1" width="39.28515625" style="66" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="68" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="68" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="212" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="68" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="68" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="116" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="68" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="68" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="68" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="68" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="68" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="68"/>
+    <col min="14" max="14" width="11.7109375" style="170" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="170" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="68" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="68" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="64" t="s">
         <v>10</v>
       </c>
@@ -2791,11 +2788,11 @@
       <c r="P1" s="65"/>
       <c r="Q1" s="65"/>
     </row>
-    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="67"/>
       <c r="G2" s="68"/>
     </row>
-    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="69"/>
       <c r="B3" s="70" t="s">
         <v>3</v>
@@ -2813,16 +2810,16 @@
         <v>12</v>
       </c>
       <c r="G3" s="72"/>
-      <c r="H3" s="228" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="M3" s="229"/>
+      <c r="H3" s="245" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="M3" s="246"/>
       <c r="N3" s="171" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O3" s="171" t="s">
         <v>6</v>
@@ -2834,7 +2831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
         <v>14</v>
       </c>
@@ -2844,142 +2841,142 @@
       <c r="C4" s="75">
         <v>18</v>
       </c>
-      <c r="D4" s="239" t="s">
+      <c r="D4" s="225" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="219" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="219" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="222" t="s">
-        <v>61</v>
+      <c r="F4" s="247" t="s">
+        <v>60</v>
       </c>
       <c r="G4" s="76" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I4" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="78" t="s">
+      <c r="K4" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="78" t="s">
-        <v>69</v>
-      </c>
       <c r="L4" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" s="79" t="s">
         <v>72</v>
-      </c>
-      <c r="M4" s="79" t="s">
-        <v>73</v>
       </c>
       <c r="N4" s="172"/>
       <c r="O4" s="172"/>
-      <c r="P4" s="226" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q4" s="226"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="217" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4" s="217"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="81"/>
       <c r="B5" s="82"/>
       <c r="C5" s="82"/>
-      <c r="D5" s="240"/>
+      <c r="D5" s="226"/>
       <c r="E5" s="220"/>
-      <c r="F5" s="223"/>
+      <c r="F5" s="248"/>
       <c r="G5" s="83"/>
       <c r="H5" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="85" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L5" s="85"/>
       <c r="M5" s="86"/>
       <c r="N5" s="166"/>
       <c r="O5" s="166"/>
-      <c r="P5" s="230"/>
-      <c r="Q5" s="230"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="241"/>
+      <c r="Q5" s="241"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81"/>
       <c r="B6" s="82"/>
       <c r="C6" s="82"/>
-      <c r="D6" s="240"/>
+      <c r="D6" s="226"/>
       <c r="E6" s="220"/>
-      <c r="F6" s="223"/>
+      <c r="F6" s="248"/>
       <c r="G6" s="83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="145" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="146" t="s">
         <v>63</v>
-      </c>
-      <c r="I6" s="146" t="s">
-        <v>64</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85"/>
       <c r="M6" s="86"/>
       <c r="N6" s="166"/>
       <c r="O6" s="166"/>
-      <c r="P6" s="230"/>
-      <c r="Q6" s="230"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="241"/>
+      <c r="Q6" s="241"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="82"/>
       <c r="C7" s="82"/>
-      <c r="D7" s="240"/>
+      <c r="D7" s="226"/>
       <c r="E7" s="220"/>
-      <c r="F7" s="223"/>
+      <c r="F7" s="248"/>
       <c r="G7" s="87" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="89" t="s">
+      <c r="J7" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="89" t="s">
-        <v>60</v>
-      </c>
       <c r="K7" s="215" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L7" s="89"/>
       <c r="M7" s="90"/>
       <c r="N7" s="205" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O7" s="166" t="s">
-        <v>130</v>
-      </c>
-      <c r="P7" s="230"/>
-      <c r="Q7" s="230"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="82"/>
       <c r="C8" s="82"/>
-      <c r="D8" s="240"/>
+      <c r="D8" s="226"/>
       <c r="E8" s="220"/>
-      <c r="F8" s="223"/>
+      <c r="F8" s="248"/>
       <c r="G8" s="91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H8" s="84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" s="85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J8" s="85"/>
       <c r="K8" s="85"/>
@@ -2987,21 +2984,21 @@
       <c r="M8" s="86"/>
       <c r="N8" s="166"/>
       <c r="O8" s="166"/>
-      <c r="P8" s="230"/>
-      <c r="Q8" s="230"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="92"/>
       <c r="B9" s="93"/>
       <c r="C9" s="93"/>
-      <c r="D9" s="241"/>
+      <c r="D9" s="227"/>
       <c r="E9" s="221"/>
-      <c r="F9" s="224"/>
+      <c r="F9" s="249"/>
       <c r="G9" s="91" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
@@ -3010,10 +3007,10 @@
       <c r="M9" s="95"/>
       <c r="N9" s="173"/>
       <c r="O9" s="173"/>
-      <c r="P9" s="231"/>
-      <c r="Q9" s="231"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="242"/>
+      <c r="Q9" s="242"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="96" t="s">
         <v>15</v>
       </c>
@@ -3023,23 +3020,23 @@
       <c r="C10" s="75">
         <v>2</v>
       </c>
-      <c r="D10" s="242" t="s">
+      <c r="D10" s="228" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="219" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="222" t="s">
-        <v>90</v>
+      <c r="F10" s="247" t="s">
+        <v>89</v>
       </c>
       <c r="G10" s="98" t="s">
         <v>0</v>
       </c>
       <c r="H10" s="99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10" s="100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J10" s="100"/>
       <c r="K10" s="100"/>
@@ -3047,18 +3044,18 @@
       <c r="M10" s="101"/>
       <c r="N10" s="172"/>
       <c r="O10" s="172"/>
-      <c r="P10" s="226" t="s">
-        <v>110</v>
+      <c r="P10" s="217" t="s">
+        <v>109</v>
       </c>
       <c r="Q10" s="102"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="81"/>
       <c r="B11" s="82"/>
       <c r="C11" s="82"/>
-      <c r="D11" s="243"/>
+      <c r="D11" s="229"/>
       <c r="E11" s="220"/>
-      <c r="F11" s="223"/>
+      <c r="F11" s="248"/>
       <c r="G11" s="83"/>
       <c r="H11" s="84"/>
       <c r="I11" s="85"/>
@@ -3068,16 +3065,16 @@
       <c r="M11" s="86"/>
       <c r="N11" s="166"/>
       <c r="O11" s="166"/>
-      <c r="P11" s="230"/>
+      <c r="P11" s="241"/>
       <c r="Q11" s="103"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="81"/>
       <c r="B12" s="82"/>
       <c r="C12" s="82"/>
-      <c r="D12" s="243"/>
+      <c r="D12" s="229"/>
       <c r="E12" s="220"/>
-      <c r="F12" s="223"/>
+      <c r="F12" s="248"/>
       <c r="G12" s="83"/>
       <c r="H12" s="84"/>
       <c r="I12" s="85"/>
@@ -3086,16 +3083,16 @@
       <c r="M12" s="86"/>
       <c r="N12" s="166"/>
       <c r="O12" s="166"/>
-      <c r="P12" s="230"/>
+      <c r="P12" s="241"/>
       <c r="Q12" s="103"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="81"/>
       <c r="B13" s="82"/>
       <c r="C13" s="82"/>
-      <c r="D13" s="243"/>
+      <c r="D13" s="229"/>
       <c r="E13" s="220"/>
-      <c r="F13" s="223"/>
+      <c r="F13" s="248"/>
       <c r="G13" s="87" t="s">
         <v>7</v>
       </c>
@@ -3107,16 +3104,16 @@
       <c r="M13" s="90"/>
       <c r="N13" s="166"/>
       <c r="O13" s="166"/>
-      <c r="P13" s="230"/>
+      <c r="P13" s="241"/>
       <c r="Q13" s="80"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="81"/>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
-      <c r="D14" s="243"/>
+      <c r="D14" s="229"/>
       <c r="E14" s="220"/>
-      <c r="F14" s="223"/>
+      <c r="F14" s="248"/>
       <c r="G14" s="91"/>
       <c r="H14" s="84"/>
       <c r="I14" s="85"/>
@@ -3126,16 +3123,16 @@
       <c r="M14" s="86"/>
       <c r="N14" s="166"/>
       <c r="O14" s="166"/>
-      <c r="P14" s="230"/>
+      <c r="P14" s="241"/>
       <c r="Q14" s="103"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="184"/>
       <c r="B15" s="112"/>
       <c r="C15" s="112"/>
-      <c r="D15" s="243"/>
+      <c r="D15" s="229"/>
       <c r="E15" s="220"/>
-      <c r="F15" s="223"/>
+      <c r="F15" s="248"/>
       <c r="G15" s="185" t="s">
         <v>1</v>
       </c>
@@ -3147,12 +3144,12 @@
       <c r="M15" s="115"/>
       <c r="N15" s="174"/>
       <c r="O15" s="174"/>
-      <c r="P15" s="231"/>
+      <c r="P15" s="242"/>
       <c r="Q15" s="103"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="186" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="198">
         <v>46089</v>
@@ -3167,34 +3164,34 @@
         <v>0</v>
       </c>
       <c r="H16" s="188" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I16" s="189" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J16" s="190" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K16" s="189" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L16" s="100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M16" s="191"/>
       <c r="N16" s="172"/>
       <c r="O16" s="199"/>
-      <c r="P16" s="226" t="s">
-        <v>110</v>
+      <c r="P16" s="217" t="s">
+        <v>109</v>
       </c>
       <c r="Q16" s="102"/>
     </row>
-    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="179"/>
       <c r="B17" s="180"/>
       <c r="C17" s="180"/>
       <c r="D17" s="157" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E17" s="154"/>
       <c r="F17" s="160"/>
@@ -3206,22 +3203,22 @@
       <c r="M17" s="183"/>
       <c r="N17" s="166"/>
       <c r="O17" s="200"/>
-      <c r="P17" s="230"/>
+      <c r="P17" s="241"/>
       <c r="Q17" s="103"/>
     </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="179"/>
       <c r="B18" s="180"/>
       <c r="C18" s="180"/>
       <c r="D18" s="157"/>
       <c r="E18" s="154" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F18" s="160" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G18" s="83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="181"/>
       <c r="J18" s="182"/>
@@ -3230,15 +3227,15 @@
       <c r="M18" s="183"/>
       <c r="N18" s="166"/>
       <c r="O18" s="200"/>
-      <c r="P18" s="230"/>
+      <c r="P18" s="241"/>
       <c r="Q18" s="103"/>
     </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="179"/>
       <c r="B19" s="180"/>
       <c r="C19" s="180"/>
       <c r="D19" s="157" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" s="154"/>
       <c r="F19" s="160"/>
@@ -3246,7 +3243,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I19" s="181"/>
       <c r="J19" s="182"/>
@@ -3255,10 +3252,10 @@
       <c r="M19" s="183"/>
       <c r="N19" s="166"/>
       <c r="O19" s="200"/>
-      <c r="P19" s="230"/>
+      <c r="P19" s="241"/>
       <c r="Q19" s="103"/>
     </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="179"/>
       <c r="B20" s="180"/>
       <c r="C20" s="180"/>
@@ -3268,7 +3265,7 @@
       <c r="E20" s="154"/>
       <c r="F20" s="160"/>
       <c r="G20" s="91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I20" s="181"/>
       <c r="J20" s="182"/>
@@ -3277,11 +3274,11 @@
       <c r="M20" s="183"/>
       <c r="N20" s="166"/>
       <c r="O20" s="201"/>
-      <c r="P20" s="230"/>
+      <c r="P20" s="241"/>
       <c r="Q20" s="103"/>
-      <c r="S20" s="234"/>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S20" s="239"/>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="192"/>
       <c r="B21" s="193"/>
       <c r="C21" s="193"/>
@@ -3299,11 +3296,11 @@
       <c r="M21" s="197"/>
       <c r="N21" s="173"/>
       <c r="O21" s="202"/>
-      <c r="P21" s="231"/>
+      <c r="P21" s="242"/>
       <c r="Q21" s="104"/>
-      <c r="S21" s="235"/>
-    </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S21" s="240"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="136" t="s">
         <v>16</v>
       </c>
@@ -3313,54 +3310,54 @@
       <c r="C22" s="75">
         <v>8</v>
       </c>
-      <c r="D22" s="244" t="s">
+      <c r="D22" s="230" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="219" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="247" t="s">
         <v>86</v>
-      </c>
-      <c r="E22" s="219" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="222" t="s">
-        <v>87</v>
       </c>
       <c r="G22" s="98" t="s">
         <v>0</v>
       </c>
       <c r="H22" s="164" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="100" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J22" s="99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K22" s="100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L22" s="99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M22" s="101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N22" s="172"/>
       <c r="O22" s="203"/>
-      <c r="P22" s="225" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q22" s="225"/>
-      <c r="S22" s="235"/>
+      <c r="P22" s="216" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q22" s="216"/>
+      <c r="S22" s="240"/>
       <c r="T22" s="105"/>
     </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="147" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="82"/>
       <c r="C23" s="82"/>
-      <c r="D23" s="245"/>
+      <c r="D23" s="231"/>
       <c r="E23" s="220"/>
-      <c r="F23" s="223"/>
+      <c r="F23" s="248"/>
       <c r="G23" s="83"/>
       <c r="H23" s="150"/>
       <c r="I23" s="78"/>
@@ -3370,25 +3367,25 @@
       <c r="M23" s="86"/>
       <c r="N23" s="166"/>
       <c r="O23" s="201"/>
-      <c r="P23" s="232"/>
-      <c r="Q23" s="232"/>
-      <c r="S23" s="235"/>
-    </row>
-    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="243"/>
+      <c r="Q23" s="243"/>
+      <c r="S23" s="240"/>
+    </row>
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="81"/>
       <c r="B24" s="82"/>
       <c r="C24" s="82"/>
-      <c r="D24" s="245"/>
+      <c r="D24" s="231"/>
       <c r="E24" s="220"/>
-      <c r="F24" s="223"/>
+      <c r="F24" s="248"/>
       <c r="G24" s="83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H24" s="150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I24" s="85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" s="85"/>
       <c r="K24" s="85"/>
@@ -3396,17 +3393,17 @@
       <c r="M24" s="86"/>
       <c r="N24" s="166"/>
       <c r="O24" s="201"/>
-      <c r="P24" s="232"/>
-      <c r="Q24" s="232"/>
-      <c r="S24" s="235"/>
-    </row>
-    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="243"/>
+      <c r="Q24" s="243"/>
+      <c r="S24" s="240"/>
+    </row>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="81"/>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
-      <c r="D25" s="245"/>
+      <c r="D25" s="231"/>
       <c r="E25" s="220"/>
-      <c r="F25" s="223"/>
+      <c r="F25" s="248"/>
       <c r="G25" s="87" t="s">
         <v>7</v>
       </c>
@@ -3418,17 +3415,17 @@
       <c r="M25" s="90"/>
       <c r="N25" s="166"/>
       <c r="O25" s="201"/>
-      <c r="P25" s="232"/>
-      <c r="Q25" s="232"/>
-      <c r="S25" s="235"/>
-    </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="243"/>
+      <c r="Q25" s="243"/>
+      <c r="S25" s="240"/>
+    </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="81"/>
       <c r="B26" s="82"/>
       <c r="C26" s="82"/>
-      <c r="D26" s="245"/>
+      <c r="D26" s="231"/>
       <c r="E26" s="220"/>
-      <c r="F26" s="223"/>
+      <c r="F26" s="248"/>
       <c r="G26" s="91"/>
       <c r="H26" s="150"/>
       <c r="I26" s="85"/>
@@ -3438,16 +3435,16 @@
       <c r="M26" s="86"/>
       <c r="N26" s="166"/>
       <c r="O26" s="200"/>
-      <c r="P26" s="232"/>
-      <c r="Q26" s="232"/>
-    </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="243"/>
+      <c r="Q26" s="243"/>
+    </row>
+    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="92"/>
       <c r="B27" s="93"/>
       <c r="C27" s="93"/>
-      <c r="D27" s="246"/>
+      <c r="D27" s="232"/>
       <c r="E27" s="221"/>
-      <c r="F27" s="224"/>
+      <c r="F27" s="249"/>
       <c r="G27" s="91" t="s">
         <v>1</v>
       </c>
@@ -3459,12 +3456,12 @@
       <c r="M27" s="95"/>
       <c r="N27" s="173"/>
       <c r="O27" s="204"/>
-      <c r="P27" s="233"/>
-      <c r="Q27" s="233"/>
-    </row>
-    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="244"/>
+      <c r="Q27" s="244"/>
+    </row>
+    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B28" s="97">
         <v>46110</v>
@@ -3472,45 +3469,45 @@
       <c r="C28" s="75">
         <v>4</v>
       </c>
-      <c r="D28" s="247" t="s">
+      <c r="D28" s="233" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="219" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="222" t="s">
-        <v>99</v>
+      <c r="F28" s="247" t="s">
+        <v>98</v>
       </c>
       <c r="G28" s="98" t="s">
         <v>0</v>
       </c>
       <c r="I28" s="99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J28" s="100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K28" s="100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L28" s="100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M28" s="101"/>
       <c r="N28" s="177"/>
       <c r="O28" s="177"/>
-      <c r="P28" s="225" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q28" s="225"/>
-    </row>
-    <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="216" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q28" s="216"/>
+    </row>
+    <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="107"/>
       <c r="B29" s="82"/>
       <c r="C29" s="82"/>
-      <c r="D29" s="248"/>
+      <c r="D29" s="234"/>
       <c r="E29" s="220"/>
-      <c r="F29" s="223"/>
+      <c r="F29" s="248"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
@@ -3520,16 +3517,16 @@
       <c r="M29" s="86"/>
       <c r="N29" s="166"/>
       <c r="O29" s="166"/>
-      <c r="P29" s="232"/>
-      <c r="Q29" s="232"/>
-    </row>
-    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="243"/>
+      <c r="Q29" s="243"/>
+    </row>
+    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="107"/>
       <c r="B30" s="82"/>
       <c r="C30" s="82"/>
-      <c r="D30" s="248"/>
+      <c r="D30" s="234"/>
       <c r="E30" s="220"/>
-      <c r="F30" s="223"/>
+      <c r="F30" s="248"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
@@ -3539,16 +3536,16 @@
       <c r="M30" s="86"/>
       <c r="N30" s="166"/>
       <c r="O30" s="166"/>
-      <c r="P30" s="232"/>
-      <c r="Q30" s="232"/>
-    </row>
-    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="243"/>
+      <c r="Q30" s="243"/>
+    </row>
+    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="107"/>
       <c r="B31" s="82"/>
       <c r="C31" s="82"/>
-      <c r="D31" s="248"/>
+      <c r="D31" s="234"/>
       <c r="E31" s="220"/>
-      <c r="F31" s="223"/>
+      <c r="F31" s="248"/>
       <c r="G31" s="87" t="s">
         <v>7</v>
       </c>
@@ -3560,16 +3557,16 @@
       <c r="M31" s="90"/>
       <c r="N31" s="166"/>
       <c r="O31" s="166"/>
-      <c r="P31" s="232"/>
-      <c r="Q31" s="232"/>
-    </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="243"/>
+      <c r="Q31" s="243"/>
+    </row>
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="107"/>
       <c r="B32" s="82"/>
       <c r="C32" s="82"/>
-      <c r="D32" s="248"/>
+      <c r="D32" s="234"/>
       <c r="E32" s="220"/>
-      <c r="F32" s="223"/>
+      <c r="F32" s="248"/>
       <c r="G32" s="91"/>
       <c r="H32" s="84"/>
       <c r="I32" s="85"/>
@@ -3579,16 +3576,16 @@
       <c r="M32" s="86"/>
       <c r="N32" s="166"/>
       <c r="O32" s="166"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="232"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="243"/>
+      <c r="Q32" s="243"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="108"/>
       <c r="B33" s="93"/>
       <c r="C33" s="93"/>
-      <c r="D33" s="249"/>
+      <c r="D33" s="235"/>
       <c r="E33" s="221"/>
-      <c r="F33" s="224"/>
+      <c r="F33" s="249"/>
       <c r="G33" s="91" t="s">
         <v>1</v>
       </c>
@@ -3600,10 +3597,10 @@
       <c r="M33" s="95"/>
       <c r="N33" s="173"/>
       <c r="O33" s="173"/>
-      <c r="P33" s="233"/>
-      <c r="Q33" s="233"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="244"/>
+      <c r="Q33" s="244"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="96" t="s">
         <v>36</v>
       </c>
@@ -3613,53 +3610,53 @@
       <c r="C34" s="75">
         <v>15</v>
       </c>
-      <c r="D34" s="216" t="s">
-        <v>119</v>
+      <c r="D34" s="236" t="s">
+        <v>118</v>
       </c>
       <c r="E34" s="219" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="222" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="F34" s="247" t="s">
+        <v>87</v>
       </c>
       <c r="G34" s="98" t="s">
         <v>0</v>
       </c>
       <c r="H34" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="I34" s="100" t="s">
+      <c r="J34" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="J34" s="100" t="s">
-        <v>65</v>
-      </c>
-      <c r="K34" s="100" t="s">
+      <c r="L34" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="L34" s="100" t="s">
+      <c r="M34" s="175" t="s">
         <v>99</v>
-      </c>
-      <c r="M34" s="175" t="s">
-        <v>100</v>
       </c>
       <c r="N34" s="178"/>
       <c r="O34" s="172"/>
-      <c r="P34" s="225" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q34" s="225"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="216" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q34" s="216"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="81"/>
       <c r="B35" s="82"/>
       <c r="C35" s="82"/>
-      <c r="D35" s="217"/>
+      <c r="D35" s="237"/>
       <c r="E35" s="220"/>
-      <c r="F35" s="223"/>
+      <c r="F35" s="248"/>
       <c r="G35" s="83"/>
       <c r="H35" s="166" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I35" s="85"/>
       <c r="J35" s="85"/>
@@ -3668,18 +3665,18 @@
       <c r="M35" s="86"/>
       <c r="N35" s="166"/>
       <c r="O35" s="166"/>
-      <c r="P35" s="226"/>
-      <c r="Q35" s="226"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P35" s="217"/>
+      <c r="Q35" s="217"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="81"/>
       <c r="B36" s="82"/>
       <c r="C36" s="82"/>
-      <c r="D36" s="217"/>
+      <c r="D36" s="237"/>
       <c r="E36" s="220"/>
-      <c r="F36" s="223"/>
+      <c r="F36" s="248"/>
       <c r="G36" s="83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H36" s="152"/>
       <c r="I36" s="85"/>
@@ -3689,74 +3686,74 @@
       <c r="M36" s="86"/>
       <c r="N36" s="166"/>
       <c r="O36" s="166"/>
-      <c r="P36" s="226"/>
-      <c r="Q36" s="226"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="217"/>
+      <c r="Q36" s="217"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="81"/>
       <c r="B37" s="82"/>
       <c r="C37" s="82"/>
-      <c r="D37" s="217"/>
+      <c r="D37" s="237"/>
       <c r="E37" s="220"/>
-      <c r="F37" s="223"/>
+      <c r="F37" s="248"/>
       <c r="G37" s="87" t="s">
         <v>7</v>
       </c>
       <c r="H37" s="162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I37" s="163" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J37" s="89" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K37" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="L37" s="89" t="s">
+      <c r="M37" s="90" t="s">
         <v>91</v>
-      </c>
-      <c r="M37" s="90" t="s">
-        <v>92</v>
       </c>
       <c r="N37" s="176"/>
       <c r="O37" s="166"/>
-      <c r="P37" s="226"/>
-      <c r="Q37" s="226"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="217"/>
+      <c r="Q37" s="217"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="81"/>
       <c r="B38" s="82"/>
       <c r="C38" s="82"/>
-      <c r="D38" s="217"/>
+      <c r="D38" s="237"/>
       <c r="E38" s="220"/>
-      <c r="F38" s="223"/>
+      <c r="F38" s="248"/>
       <c r="G38" s="91"/>
       <c r="H38" s="165" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="I38" s="163" t="s">
-        <v>95</v>
-      </c>
       <c r="J38" s="90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K38" s="85"/>
       <c r="L38" s="85"/>
       <c r="M38" s="86"/>
       <c r="N38" s="166"/>
       <c r="O38" s="166"/>
-      <c r="P38" s="226"/>
-      <c r="Q38" s="226"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="217"/>
+      <c r="Q38" s="217"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="92"/>
       <c r="B39" s="93"/>
       <c r="C39" s="93"/>
-      <c r="D39" s="218"/>
+      <c r="D39" s="238"/>
       <c r="E39" s="221"/>
-      <c r="F39" s="224"/>
+      <c r="F39" s="249"/>
       <c r="G39" s="91" t="s">
         <v>1</v>
       </c>
@@ -3768,10 +3765,10 @@
       <c r="M39" s="95"/>
       <c r="N39" s="173"/>
       <c r="O39" s="173"/>
-      <c r="P39" s="227"/>
-      <c r="Q39" s="227"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P39" s="218"/>
+      <c r="Q39" s="218"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="96" t="s">
         <v>5</v>
       </c>
@@ -3782,94 +3779,94 @@
         <v>18</v>
       </c>
       <c r="D40" s="213"/>
-      <c r="E40" s="236" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" s="222" t="s">
-        <v>88</v>
+      <c r="E40" s="222" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="247" t="s">
+        <v>87</v>
       </c>
       <c r="G40" s="98" t="s">
         <v>0</v>
       </c>
       <c r="H40" s="68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I40" s="85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J40" s="100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K40" s="100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L40" s="100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M40" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N40" s="206" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O40" s="207" t="s">
-        <v>128</v>
-      </c>
-      <c r="P40" s="225" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q40" s="225"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="P40" s="216" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q40" s="216"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="107"/>
       <c r="B41" s="82"/>
       <c r="C41" s="209"/>
       <c r="D41" s="157" t="s">
-        <v>114</v>
-      </c>
-      <c r="E41" s="237"/>
-      <c r="F41" s="223"/>
+        <v>113</v>
+      </c>
+      <c r="E41" s="223"/>
+      <c r="F41" s="248"/>
       <c r="G41" s="83"/>
       <c r="H41" s="84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I41" s="175" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J41" s="166" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K41" s="85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L41" s="85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M41" s="206" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N41" s="166"/>
       <c r="O41" s="166"/>
-      <c r="P41" s="226"/>
-      <c r="Q41" s="226"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="217"/>
+      <c r="Q41" s="217"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="107"/>
       <c r="B42" s="82"/>
       <c r="C42" s="209"/>
       <c r="D42" s="157" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="237"/>
-      <c r="F42" s="223"/>
+        <v>114</v>
+      </c>
+      <c r="E42" s="223"/>
+      <c r="F42" s="248"/>
       <c r="G42" s="83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H42" s="167" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I42" s="168" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J42" s="85"/>
       <c r="K42" s="85"/>
@@ -3877,51 +3874,51 @@
       <c r="M42" s="86"/>
       <c r="N42" s="166"/>
       <c r="O42" s="166"/>
-      <c r="P42" s="226"/>
-      <c r="Q42" s="226"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="217"/>
+      <c r="Q42" s="217"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="107"/>
       <c r="B43" s="82"/>
       <c r="C43" s="209"/>
       <c r="D43" s="157" t="s">
-        <v>113</v>
-      </c>
-      <c r="E43" s="237"/>
-      <c r="F43" s="223"/>
+        <v>112</v>
+      </c>
+      <c r="E43" s="223"/>
+      <c r="F43" s="248"/>
       <c r="G43" s="87" t="s">
         <v>7</v>
       </c>
       <c r="H43" s="109" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I43" s="110" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J43" s="110" t="s">
+        <v>100</v>
+      </c>
+      <c r="K43" s="110" t="s">
         <v>101</v>
       </c>
-      <c r="K43" s="110" t="s">
-        <v>102</v>
-      </c>
       <c r="L43" s="215" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M43" s="111"/>
       <c r="N43" s="166"/>
       <c r="O43" s="166"/>
-      <c r="P43" s="226"/>
-      <c r="Q43" s="226"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="217"/>
+      <c r="Q43" s="217"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="107"/>
       <c r="B44" s="82"/>
       <c r="C44" s="209"/>
       <c r="D44" s="157">
         <v>33</v>
       </c>
-      <c r="E44" s="237"/>
-      <c r="F44" s="223"/>
+      <c r="E44" s="223"/>
+      <c r="F44" s="248"/>
       <c r="G44" s="91"/>
       <c r="H44" s="84"/>
       <c r="I44" s="85"/>
@@ -3931,16 +3928,16 @@
       <c r="M44" s="86"/>
       <c r="N44" s="166"/>
       <c r="O44" s="166"/>
-      <c r="P44" s="226"/>
-      <c r="Q44" s="226"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="217"/>
+      <c r="Q44" s="217"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="108"/>
       <c r="B45" s="93"/>
       <c r="C45" s="211"/>
       <c r="D45" s="158"/>
-      <c r="E45" s="238"/>
-      <c r="F45" s="224"/>
+      <c r="E45" s="224"/>
+      <c r="F45" s="249"/>
       <c r="G45" s="91" t="s">
         <v>1</v>
       </c>
@@ -3952,59 +3949,59 @@
       <c r="M45" s="95"/>
       <c r="N45" s="173"/>
       <c r="O45" s="173"/>
-      <c r="P45" s="227"/>
-      <c r="Q45" s="227"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="218"/>
+      <c r="Q45" s="218"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="136" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="97">
         <v>46110</v>
       </c>
       <c r="C46" s="75"/>
-      <c r="D46" s="216" t="s">
-        <v>122</v>
+      <c r="D46" s="236" t="s">
+        <v>121</v>
       </c>
       <c r="E46" s="219" t="s">
-        <v>121</v>
-      </c>
-      <c r="F46" s="222" t="s">
-        <v>89</v>
+        <v>120</v>
+      </c>
+      <c r="F46" s="247" t="s">
+        <v>88</v>
       </c>
       <c r="G46" s="98" t="s">
         <v>0</v>
       </c>
       <c r="H46" s="99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I46" s="100" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J46" s="100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K46" s="100" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L46" s="100"/>
       <c r="M46" s="101"/>
       <c r="N46" s="172"/>
       <c r="O46" s="172"/>
-      <c r="P46" s="225" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q46" s="225"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="216" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q46" s="216"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="82"/>
       <c r="C47" s="82"/>
-      <c r="D47" s="217"/>
+      <c r="D47" s="237"/>
       <c r="E47" s="220"/>
-      <c r="F47" s="223"/>
+      <c r="F47" s="248"/>
       <c r="G47" s="83"/>
       <c r="H47" s="84"/>
       <c r="I47" s="85"/>
@@ -4014,19 +4011,19 @@
       <c r="M47" s="86"/>
       <c r="N47" s="166"/>
       <c r="O47" s="166"/>
-      <c r="P47" s="226"/>
-      <c r="Q47" s="226"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="217"/>
+      <c r="Q47" s="217"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="107"/>
       <c r="B48" s="82"/>
       <c r="C48" s="82"/>
-      <c r="D48" s="217"/>
+      <c r="D48" s="237"/>
       <c r="E48" s="220"/>
-      <c r="F48" s="223"/>
+      <c r="F48" s="248"/>
       <c r="G48" s="83"/>
       <c r="H48" s="84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I48" s="85"/>
       <c r="J48" s="85"/>
@@ -4035,24 +4032,24 @@
       <c r="M48" s="86"/>
       <c r="N48" s="166"/>
       <c r="O48" s="166"/>
-      <c r="P48" s="226"/>
-      <c r="Q48" s="226"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="217"/>
+      <c r="Q48" s="217"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="107"/>
       <c r="B49" s="82"/>
       <c r="C49" s="82"/>
-      <c r="D49" s="217"/>
+      <c r="D49" s="237"/>
       <c r="E49" s="220"/>
-      <c r="F49" s="223"/>
+      <c r="F49" s="248"/>
       <c r="G49" s="87" t="s">
         <v>7</v>
       </c>
       <c r="H49" s="110" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I49" s="214" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J49" s="110"/>
       <c r="K49" s="110"/>
@@ -4060,18 +4057,18 @@
       <c r="M49" s="111"/>
       <c r="N49" s="166"/>
       <c r="O49" s="208" t="s">
-        <v>120</v>
-      </c>
-      <c r="P49" s="226"/>
-      <c r="Q49" s="226"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+      <c r="P49" s="217"/>
+      <c r="Q49" s="217"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="107"/>
       <c r="B50" s="82"/>
       <c r="C50" s="82"/>
-      <c r="D50" s="217"/>
+      <c r="D50" s="237"/>
       <c r="E50" s="220"/>
-      <c r="F50" s="223"/>
+      <c r="F50" s="248"/>
       <c r="G50" s="91"/>
       <c r="H50" s="84"/>
       <c r="I50" s="85"/>
@@ -4081,16 +4078,16 @@
       <c r="M50" s="86"/>
       <c r="N50" s="166"/>
       <c r="O50" s="166"/>
-      <c r="P50" s="226"/>
-      <c r="Q50" s="226"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="217"/>
+      <c r="Q50" s="217"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="108"/>
       <c r="B51" s="93"/>
       <c r="C51" s="93"/>
-      <c r="D51" s="218"/>
+      <c r="D51" s="238"/>
       <c r="E51" s="221"/>
-      <c r="F51" s="224"/>
+      <c r="F51" s="249"/>
       <c r="G51" s="91" t="s">
         <v>1</v>
       </c>
@@ -4102,29 +4099,19 @@
       <c r="M51" s="95"/>
       <c r="N51" s="173"/>
       <c r="O51" s="173"/>
-      <c r="P51" s="227"/>
-      <c r="Q51" s="227"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P51" s="218"/>
+      <c r="Q51" s="218"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="L55" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="P34:P39"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="E40:E45"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="S20:S25"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D46:D51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="P46:P51"/>
+    <mergeCell ref="Q46:Q51"/>
     <mergeCell ref="H3:M3"/>
     <mergeCell ref="Q40:Q45"/>
     <mergeCell ref="F4:F9"/>
@@ -4141,11 +4128,21 @@
     <mergeCell ref="P16:P21"/>
     <mergeCell ref="P40:P45"/>
     <mergeCell ref="P28:P33"/>
-    <mergeCell ref="D46:D51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="P46:P51"/>
-    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="S20:S25"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="P34:P39"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="E40:E45"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="D34:D39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="115" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4159,25 +4156,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -4198,11 +4195,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -4237,7 +4234,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>17</v>
       </c>
@@ -4247,9 +4244,9 @@
       <c r="C4" s="46">
         <v>10</v>
       </c>
-      <c r="D4" s="250"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="256"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="263"/>
       <c r="G4" s="28" t="s">
         <v>0</v>
       </c>
@@ -4261,16 +4258,16 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="264"/>
       <c r="G5" s="23"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2"/>
@@ -4280,16 +4277,16 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="23"/>
       <c r="H6" s="15"/>
       <c r="I6" s="2"/>
@@ -4298,16 +4295,16 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="20" t="s">
         <v>7</v>
       </c>
@@ -4319,16 +4316,16 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
-      <c r="D8" s="251"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="19"/>
       <c r="H8" s="15"/>
       <c r="I8" s="2"/>
@@ -4338,16 +4335,16 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="265"/>
       <c r="G9" s="19" t="s">
         <v>1</v>
       </c>
@@ -4359,10 +4356,10 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>18</v>
       </c>
@@ -4372,9 +4369,9 @@
       <c r="C10" s="46">
         <v>16</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -4389,13 +4386,13 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -4408,13 +4405,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -4426,13 +4423,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -4447,13 +4444,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -4466,13 +4463,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -4487,9 +4484,9 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="53">
         <v>46138</v>
@@ -4497,9 +4494,9 @@
       <c r="C16" s="1">
         <v>2</v>
       </c>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -4511,17 +4508,17 @@
       <c r="M16" s="5"/>
       <c r="N16" s="8"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
+      <c r="P16" s="250"/>
+      <c r="Q16" s="250"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -4531,16 +4528,16 @@
       <c r="M17" s="2"/>
       <c r="N17" s="9"/>
       <c r="O17" s="49"/>
-      <c r="P17" s="263"/>
-      <c r="Q17" s="263"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="255"/>
+      <c r="Q17" s="255"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -4550,16 +4547,16 @@
       <c r="M18" s="2"/>
       <c r="N18" s="9"/>
       <c r="O18" s="49"/>
-      <c r="P18" s="263"/>
-      <c r="Q18" s="263"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="255"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -4571,16 +4568,16 @@
       <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="62"/>
-      <c r="P19" s="263"/>
-      <c r="Q19" s="263"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="255"/>
+      <c r="Q19" s="255"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -4590,16 +4587,16 @@
       <c r="M20" s="2"/>
       <c r="N20" s="9"/>
       <c r="O20" s="49"/>
-      <c r="P20" s="263"/>
-      <c r="Q20" s="263"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="255"/>
+      <c r="Q20" s="255"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -4611,10 +4608,10 @@
       <c r="M21" s="6"/>
       <c r="N21" s="10"/>
       <c r="O21" s="51"/>
-      <c r="P21" s="264"/>
-      <c r="Q21" s="264"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="256"/>
+      <c r="Q21" s="256"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>19</v>
       </c>
@@ -4624,9 +4621,9 @@
       <c r="C22" s="46">
         <v>18</v>
       </c>
-      <c r="D22" s="250"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="22" t="s">
         <v>0</v>
       </c>
@@ -4638,16 +4635,16 @@
       <c r="M22" s="5"/>
       <c r="N22" s="8"/>
       <c r="O22" s="47"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="250"/>
+      <c r="Q22" s="250"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="257"/>
+      <c r="D23" s="258"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="264"/>
       <c r="G23" s="23"/>
       <c r="H23" s="15"/>
       <c r="I23" s="2"/>
@@ -4657,16 +4654,16 @@
       <c r="M23" s="2"/>
       <c r="N23" s="9"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="263"/>
-      <c r="Q23" s="263"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="255"/>
+      <c r="Q23" s="255"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="264"/>
       <c r="G24" s="23"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2"/>
@@ -4676,16 +4673,16 @@
       <c r="M24" s="2"/>
       <c r="N24" s="9"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="263"/>
-      <c r="Q24" s="263"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="255"/>
+      <c r="Q24" s="255"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="257"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="264"/>
       <c r="G25" s="20" t="s">
         <v>7</v>
       </c>
@@ -4697,16 +4694,16 @@
       <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="62"/>
-      <c r="P25" s="263"/>
-      <c r="Q25" s="263"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="255"/>
+      <c r="Q25" s="255"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="251"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="257"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="264"/>
       <c r="G26" s="19"/>
       <c r="H26" s="15"/>
       <c r="I26" s="2"/>
@@ -4716,16 +4713,16 @@
       <c r="M26" s="2"/>
       <c r="N26" s="9"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="263"/>
-      <c r="Q26" s="263"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="255"/>
+      <c r="Q26" s="255"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="265"/>
       <c r="G27" s="19" t="s">
         <v>1</v>
       </c>
@@ -4737,16 +4734,16 @@
       <c r="M27" s="6"/>
       <c r="N27" s="10"/>
       <c r="O27" s="51"/>
-      <c r="P27" s="264"/>
-      <c r="Q27" s="264"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
       <c r="B28" s="53"/>
       <c r="C28" s="46"/>
-      <c r="D28" s="250"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="256"/>
+      <c r="D28" s="257"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="263"/>
       <c r="G28" s="22" t="s">
         <v>0</v>
       </c>
@@ -4758,16 +4755,16 @@
       <c r="M28" s="5"/>
       <c r="N28" s="8"/>
       <c r="O28" s="47"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="250"/>
+      <c r="Q28" s="250"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="254"/>
-      <c r="F29" s="257"/>
+      <c r="D29" s="258"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="264"/>
       <c r="G29" s="23"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -4777,16 +4774,16 @@
       <c r="M29" s="2"/>
       <c r="N29" s="9"/>
       <c r="O29" s="49"/>
-      <c r="P29" s="259"/>
-      <c r="Q29" s="259"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="254"/>
-      <c r="F30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="261"/>
+      <c r="F30" s="264"/>
       <c r="G30" s="23"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -4796,16 +4793,16 @@
       <c r="M30" s="2"/>
       <c r="N30" s="9"/>
       <c r="O30" s="49"/>
-      <c r="P30" s="259"/>
-      <c r="Q30" s="259"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="261"/>
+      <c r="F31" s="264"/>
       <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
@@ -4817,16 +4814,16 @@
       <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="62"/>
-      <c r="P31" s="259"/>
-      <c r="Q31" s="259"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="251"/>
+      <c r="Q31" s="251"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
-      <c r="D32" s="251"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="264"/>
       <c r="G32" s="19"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -4836,16 +4833,16 @@
       <c r="M32" s="2"/>
       <c r="N32" s="9"/>
       <c r="O32" s="49"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="251"/>
+      <c r="Q32" s="251"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="265"/>
       <c r="G33" s="19" t="s">
         <v>1</v>
       </c>
@@ -4857,16 +4854,16 @@
       <c r="M33" s="6"/>
       <c r="N33" s="10"/>
       <c r="O33" s="51"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="265"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="53"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="256"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="263"/>
       <c r="G34" s="22" t="s">
         <v>0</v>
       </c>
@@ -4878,16 +4875,16 @@
       <c r="M34" s="5"/>
       <c r="N34" s="8"/>
       <c r="O34" s="47"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="250"/>
+      <c r="Q34" s="250"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="258"/>
+      <c r="E35" s="261"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="23"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -4897,16 +4894,16 @@
       <c r="M35" s="2"/>
       <c r="N35" s="9"/>
       <c r="O35" s="49"/>
-      <c r="P35" s="259"/>
-      <c r="Q35" s="259"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="251"/>
+      <c r="Q35" s="251"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="257"/>
+      <c r="D36" s="258"/>
+      <c r="E36" s="261"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="23"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -4916,16 +4913,16 @@
       <c r="M36" s="2"/>
       <c r="N36" s="9"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="251"/>
+      <c r="Q36" s="251"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
-      <c r="D37" s="251"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="257"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="261"/>
+      <c r="F37" s="264"/>
       <c r="G37" s="20" t="s">
         <v>7</v>
       </c>
@@ -4937,16 +4934,16 @@
       <c r="M37" s="25"/>
       <c r="N37" s="26"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="251"/>
+      <c r="Q37" s="251"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="251"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="257"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="261"/>
+      <c r="F38" s="264"/>
       <c r="G38" s="19"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -4956,16 +4953,16 @@
       <c r="M38" s="2"/>
       <c r="N38" s="9"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="251"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="258"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="265"/>
       <c r="G39" s="19" t="s">
         <v>1</v>
       </c>
@@ -4977,16 +4974,16 @@
       <c r="M39" s="6"/>
       <c r="N39" s="10"/>
       <c r="O39" s="51"/>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="265"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="252"/>
+      <c r="Q39" s="252"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="256"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="263"/>
       <c r="G40" s="22" t="s">
         <v>0</v>
       </c>
@@ -4998,16 +4995,16 @@
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="47"/>
-      <c r="P40" s="262"/>
-      <c r="Q40" s="262"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="257"/>
+      <c r="D41" s="258"/>
+      <c r="E41" s="261"/>
+      <c r="F41" s="264"/>
       <c r="G41" s="23"/>
       <c r="H41" s="15"/>
       <c r="I41" s="2"/>
@@ -5017,16 +5014,16 @@
       <c r="M41" s="2"/>
       <c r="N41" s="9"/>
       <c r="O41" s="49"/>
-      <c r="P41" s="259"/>
-      <c r="Q41" s="259"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="251"/>
+      <c r="Q41" s="251"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="257"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="264"/>
       <c r="G42" s="23"/>
       <c r="H42" s="15"/>
       <c r="I42" s="2"/>
@@ -5036,16 +5033,16 @@
       <c r="M42" s="2"/>
       <c r="N42" s="9"/>
       <c r="O42" s="49"/>
-      <c r="P42" s="259"/>
-      <c r="Q42" s="259"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="251"/>
+      <c r="Q42" s="251"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="251"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="257"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="261"/>
+      <c r="F43" s="264"/>
       <c r="G43" s="20" t="s">
         <v>7</v>
       </c>
@@ -5057,16 +5054,16 @@
       <c r="M43" s="25"/>
       <c r="N43" s="26"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="259"/>
-      <c r="Q43" s="259"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="251"/>
+      <c r="Q43" s="251"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="251"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="257"/>
+      <c r="D44" s="258"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="264"/>
       <c r="G44" s="19"/>
       <c r="H44" s="15"/>
       <c r="I44" s="2"/>
@@ -5076,16 +5073,16 @@
       <c r="M44" s="2"/>
       <c r="N44" s="9"/>
       <c r="O44" s="49"/>
-      <c r="P44" s="259"/>
-      <c r="Q44" s="259"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="251"/>
+      <c r="Q44" s="251"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="252"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="258"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="265"/>
       <c r="G45" s="19" t="s">
         <v>1</v>
       </c>
@@ -5097,16 +5094,16 @@
       <c r="M45" s="6"/>
       <c r="N45" s="10"/>
       <c r="O45" s="51"/>
-      <c r="P45" s="265"/>
-      <c r="Q45" s="265"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="252"/>
+      <c r="Q45" s="252"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="253"/>
-      <c r="F46" s="256"/>
+      <c r="D46" s="257"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="263"/>
       <c r="G46" s="22" t="s">
         <v>0</v>
       </c>
@@ -5118,16 +5115,16 @@
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="47"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="262"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="250"/>
+      <c r="Q46" s="250"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
-      <c r="D47" s="251"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="257"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="261"/>
+      <c r="F47" s="264"/>
       <c r="G47" s="23"/>
       <c r="H47" s="15"/>
       <c r="I47" s="2"/>
@@ -5137,16 +5134,16 @@
       <c r="M47" s="2"/>
       <c r="N47" s="9"/>
       <c r="O47" s="49"/>
-      <c r="P47" s="259"/>
-      <c r="Q47" s="259"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="251"/>
+      <c r="Q47" s="251"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
-      <c r="D48" s="251"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="257"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="261"/>
+      <c r="F48" s="264"/>
       <c r="G48" s="23"/>
       <c r="H48" s="15"/>
       <c r="I48" s="2"/>
@@ -5156,16 +5153,16 @@
       <c r="M48" s="2"/>
       <c r="N48" s="9"/>
       <c r="O48" s="49"/>
-      <c r="P48" s="259"/>
-      <c r="Q48" s="259"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="251"/>
+      <c r="Q48" s="251"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="257"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="261"/>
+      <c r="F49" s="264"/>
       <c r="G49" s="20" t="s">
         <v>7</v>
       </c>
@@ -5177,16 +5174,16 @@
       <c r="M49" s="25"/>
       <c r="N49" s="26"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="259"/>
-      <c r="Q49" s="259"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P49" s="251"/>
+      <c r="Q49" s="251"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="257"/>
+      <c r="D50" s="258"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="264"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
       <c r="I50" s="4"/>
@@ -5196,16 +5193,16 @@
       <c r="M50" s="4"/>
       <c r="N50" s="11"/>
       <c r="O50" s="52"/>
-      <c r="P50" s="259"/>
-      <c r="Q50" s="259"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="251"/>
+      <c r="Q50" s="251"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
-      <c r="D51" s="252"/>
-      <c r="E51" s="255"/>
-      <c r="F51" s="258"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="265"/>
       <c r="G51" s="21" t="s">
         <v>1</v>
       </c>
@@ -5217,18 +5214,34 @@
       <c r="M51" s="6"/>
       <c r="N51" s="10"/>
       <c r="O51" s="51"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="265"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="Q40:Q45"/>
-    <mergeCell ref="Q46:Q51"/>
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="Q16:Q21"/>
-    <mergeCell ref="Q22:Q27"/>
-    <mergeCell ref="Q28:Q33"/>
-    <mergeCell ref="Q34:Q39"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="P28:P33"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="P34:P39"/>
     <mergeCell ref="D40:D45"/>
     <mergeCell ref="E40:E45"/>
     <mergeCell ref="F40:F45"/>
@@ -5237,29 +5250,13 @@
     <mergeCell ref="E46:E51"/>
     <mergeCell ref="F46:F51"/>
     <mergeCell ref="P46:P51"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="P34:P39"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="P16:P21"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="P22:P27"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="Q40:Q45"/>
+    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="Q16:Q21"/>
+    <mergeCell ref="Q22:Q27"/>
+    <mergeCell ref="Q28:Q33"/>
+    <mergeCell ref="Q34:Q39"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5270,25 +5267,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE98D2DE-C6E0-479C-8B63-4200FD8D2A5E}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -5309,11 +5306,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -5348,7 +5345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>20</v>
       </c>
@@ -5358,9 +5355,9 @@
       <c r="C4" s="46">
         <v>9</v>
       </c>
-      <c r="D4" s="250"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="256"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="263"/>
       <c r="G4" s="28" t="s">
         <v>0</v>
       </c>
@@ -5372,16 +5369,16 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="264"/>
       <c r="G5" s="23"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2"/>
@@ -5391,16 +5388,16 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="23"/>
       <c r="H6" s="15"/>
       <c r="I6" s="2"/>
@@ -5409,16 +5406,16 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="20" t="s">
         <v>7</v>
       </c>
@@ -5430,16 +5427,16 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
-      <c r="D8" s="251"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="19"/>
       <c r="H8" s="15"/>
       <c r="I8" s="2"/>
@@ -5449,16 +5446,16 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="265"/>
       <c r="G9" s="19" t="s">
         <v>1</v>
       </c>
@@ -5470,10 +5467,10 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>21</v>
       </c>
@@ -5483,9 +5480,9 @@
       <c r="C10" s="46">
         <v>24</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -5500,13 +5497,13 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -5519,13 +5516,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -5537,13 +5534,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -5558,13 +5555,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -5577,13 +5574,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -5598,7 +5595,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>22</v>
       </c>
@@ -5608,9 +5605,9 @@
       <c r="C16" s="46">
         <v>7</v>
       </c>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -5625,13 +5622,13 @@
       <c r="P16" s="59"/>
       <c r="Q16" s="59"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="127"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -5644,13 +5641,13 @@
       <c r="P17" s="60"/>
       <c r="Q17" s="60"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -5662,13 +5659,13 @@
       <c r="P18" s="60"/>
       <c r="Q18" s="60"/>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -5683,13 +5680,13 @@
       <c r="P19" s="58"/>
       <c r="Q19" s="58"/>
     </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -5702,13 +5699,13 @@
       <c r="P20" s="60"/>
       <c r="Q20" s="60"/>
     </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -5723,9 +5720,9 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="53">
         <v>46156</v>
@@ -5750,7 +5747,7 @@
       <c r="P22" s="59"/>
       <c r="Q22" s="59"/>
     </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="38"/>
       <c r="B23" s="127"/>
       <c r="C23" s="48"/>
@@ -5769,7 +5766,7 @@
       <c r="P23" s="60"/>
       <c r="Q23" s="60"/>
     </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="38"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -5787,7 +5784,7 @@
       <c r="P24" s="60"/>
       <c r="Q24" s="60"/>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="38"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -5808,7 +5805,7 @@
       <c r="P25" s="58"/>
       <c r="Q25" s="58"/>
     </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="38"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -5827,7 +5824,7 @@
       <c r="P26" s="60"/>
       <c r="Q26" s="60"/>
     </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
@@ -5848,17 +5845,17 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="53">
         <v>46156</v>
       </c>
       <c r="C28" s="138"/>
       <c r="D28" s="266"/>
-      <c r="E28" s="267"/>
-      <c r="F28" s="269"/>
+      <c r="E28" s="271"/>
+      <c r="F28" s="272"/>
       <c r="G28" s="141" t="s">
         <v>0</v>
       </c>
@@ -5873,13 +5870,13 @@
       <c r="P28" s="59"/>
       <c r="Q28" s="59"/>
     </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="38"/>
       <c r="B29" s="127"/>
       <c r="C29" s="139"/>
       <c r="D29" s="266"/>
-      <c r="E29" s="268"/>
-      <c r="F29" s="270"/>
+      <c r="E29" s="267"/>
+      <c r="F29" s="269"/>
       <c r="G29" s="142"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -5892,13 +5889,13 @@
       <c r="P29" s="60"/>
       <c r="Q29" s="60"/>
     </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="139"/>
       <c r="D30" s="266"/>
-      <c r="E30" s="268"/>
-      <c r="F30" s="270"/>
+      <c r="E30" s="267"/>
+      <c r="F30" s="269"/>
       <c r="G30" s="142"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -5910,17 +5907,17 @@
       <c r="P30" s="60"/>
       <c r="Q30" s="60"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="127">
         <v>46157</v>
       </c>
       <c r="C31" s="139"/>
       <c r="D31" s="266"/>
-      <c r="E31" s="268"/>
-      <c r="F31" s="270"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="269"/>
       <c r="G31" s="143" t="s">
         <v>7</v>
       </c>
@@ -5935,13 +5932,13 @@
       <c r="P31" s="58"/>
       <c r="Q31" s="58"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="139"/>
       <c r="D32" s="266"/>
-      <c r="E32" s="268"/>
-      <c r="F32" s="270"/>
+      <c r="E32" s="267"/>
+      <c r="F32" s="269"/>
       <c r="G32" s="144"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -5954,13 +5951,13 @@
       <c r="P32" s="60"/>
       <c r="Q32" s="60"/>
     </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="140"/>
       <c r="D33" s="266"/>
-      <c r="E33" s="268"/>
-      <c r="F33" s="270"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="269"/>
       <c r="G33" s="144" t="s">
         <v>1</v>
       </c>
@@ -5975,9 +5972,9 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="137" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="53">
         <v>46166</v>
@@ -5985,9 +5982,9 @@
       <c r="C34" s="138">
         <v>12</v>
       </c>
-      <c r="D34" s="252"/>
-      <c r="E34" s="268"/>
-      <c r="F34" s="270"/>
+      <c r="D34" s="259"/>
+      <c r="E34" s="267"/>
+      <c r="F34" s="269"/>
       <c r="G34" s="141" t="s">
         <v>0</v>
       </c>
@@ -6002,15 +5999,15 @@
       <c r="P34" s="59"/>
       <c r="Q34" s="59"/>
     </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="149" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="127"/>
       <c r="C35" s="139"/>
       <c r="D35" s="266"/>
-      <c r="E35" s="268"/>
-      <c r="F35" s="270"/>
+      <c r="E35" s="267"/>
+      <c r="F35" s="269"/>
       <c r="G35" s="142"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -6023,13 +6020,13 @@
       <c r="P35" s="60"/>
       <c r="Q35" s="60"/>
     </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="38"/>
       <c r="B36" s="48"/>
       <c r="C36" s="139"/>
       <c r="D36" s="266"/>
-      <c r="E36" s="268"/>
-      <c r="F36" s="270"/>
+      <c r="E36" s="267"/>
+      <c r="F36" s="269"/>
       <c r="G36" s="142"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -6041,13 +6038,13 @@
       <c r="P36" s="60"/>
       <c r="Q36" s="60"/>
     </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="38"/>
       <c r="B37" s="48"/>
       <c r="C37" s="139"/>
       <c r="D37" s="266"/>
-      <c r="E37" s="268"/>
-      <c r="F37" s="270"/>
+      <c r="E37" s="267"/>
+      <c r="F37" s="269"/>
       <c r="G37" s="143" t="s">
         <v>7</v>
       </c>
@@ -6062,13 +6059,13 @@
       <c r="P37" s="58"/>
       <c r="Q37" s="58"/>
     </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="38"/>
       <c r="B38" s="48"/>
       <c r="C38" s="139"/>
       <c r="D38" s="266"/>
-      <c r="E38" s="268"/>
-      <c r="F38" s="270"/>
+      <c r="E38" s="267"/>
+      <c r="F38" s="269"/>
       <c r="G38" s="144"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -6081,13 +6078,13 @@
       <c r="P38" s="60"/>
       <c r="Q38" s="60"/>
     </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="39"/>
       <c r="B39" s="50"/>
       <c r="C39" s="140"/>
       <c r="D39" s="266"/>
-      <c r="E39" s="271"/>
-      <c r="F39" s="272"/>
+      <c r="E39" s="268"/>
+      <c r="F39" s="270"/>
       <c r="G39" s="144" t="s">
         <v>1</v>
       </c>
@@ -6102,7 +6099,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>23</v>
       </c>
@@ -6129,7 +6126,7 @@
       <c r="P40" s="133"/>
       <c r="Q40" s="133"/>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
@@ -6148,7 +6145,7 @@
       <c r="P41" s="134"/>
       <c r="Q41" s="134"/>
     </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
@@ -6167,7 +6164,7 @@
       <c r="P42" s="134"/>
       <c r="Q42" s="134"/>
     </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
@@ -6188,7 +6185,7 @@
       <c r="P43" s="134"/>
       <c r="Q43" s="134"/>
     </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -6207,7 +6204,7 @@
       <c r="P44" s="134"/>
       <c r="Q44" s="134"/>
     </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
@@ -6228,7 +6225,7 @@
       <c r="P45" s="135"/>
       <c r="Q45" s="135"/>
     </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
         <v>23</v>
       </c>
@@ -6255,7 +6252,7 @@
       <c r="P46" s="133"/>
       <c r="Q46" s="133"/>
     </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
@@ -6274,7 +6271,7 @@
       <c r="P47" s="134"/>
       <c r="Q47" s="134"/>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
@@ -6293,7 +6290,7 @@
       <c r="P48" s="134"/>
       <c r="Q48" s="134"/>
     </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
@@ -6314,7 +6311,7 @@
       <c r="P49" s="134"/>
       <c r="Q49" s="134"/>
     </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="41"/>
       <c r="B50" s="48"/>
       <c r="C50" s="48"/>
@@ -6333,7 +6330,7 @@
       <c r="P50" s="134"/>
       <c r="Q50" s="134"/>
     </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
@@ -6354,9 +6351,9 @@
       <c r="P51" s="135"/>
       <c r="Q51" s="135"/>
     </row>
-    <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="127">
         <v>46172</v>
@@ -6381,7 +6378,7 @@
       <c r="P52" s="133"/>
       <c r="Q52" s="133"/>
     </row>
-    <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="41"/>
       <c r="B53" s="127">
         <v>46173</v>
@@ -6404,7 +6401,7 @@
       <c r="P53" s="134"/>
       <c r="Q53" s="134"/>
     </row>
-    <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="41"/>
       <c r="B54" s="127"/>
       <c r="C54" s="48"/>
@@ -6423,7 +6420,7 @@
       <c r="P54" s="134"/>
       <c r="Q54" s="134"/>
     </row>
-    <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="41"/>
       <c r="B55" s="48"/>
       <c r="C55" s="48"/>
@@ -6444,7 +6441,7 @@
       <c r="P55" s="134"/>
       <c r="Q55" s="134"/>
     </row>
-    <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="44"/>
       <c r="B56" s="54"/>
       <c r="C56" s="54"/>
@@ -6463,7 +6460,7 @@
       <c r="P56" s="134"/>
       <c r="Q56" s="134"/>
     </row>
-    <row r="57" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="42"/>
       <c r="B57" s="50"/>
       <c r="C57" s="50"/>
@@ -6484,9 +6481,9 @@
       <c r="P57" s="135"/>
       <c r="Q57" s="135"/>
     </row>
-    <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="53">
         <v>46173</v>
@@ -6511,7 +6508,7 @@
       <c r="P58" s="133"/>
       <c r="Q58" s="133"/>
     </row>
-    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="41"/>
       <c r="B59" s="49"/>
       <c r="C59" s="48"/>
@@ -6530,7 +6527,7 @@
       <c r="P59" s="134"/>
       <c r="Q59" s="134"/>
     </row>
-    <row r="60" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41"/>
       <c r="B60" s="127"/>
       <c r="C60" s="48"/>
@@ -6549,7 +6546,7 @@
       <c r="P60" s="134"/>
       <c r="Q60" s="134"/>
     </row>
-    <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="41"/>
       <c r="B61" s="48"/>
       <c r="C61" s="48"/>
@@ -6570,7 +6567,7 @@
       <c r="P61" s="134"/>
       <c r="Q61" s="134"/>
     </row>
-    <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="44"/>
       <c r="B62" s="127"/>
       <c r="C62" s="54"/>
@@ -6589,7 +6586,7 @@
       <c r="P62" s="134"/>
       <c r="Q62" s="134"/>
     </row>
-    <row r="63" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="42"/>
       <c r="B63" s="50"/>
       <c r="C63" s="50"/>
@@ -6612,12 +6609,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
     <mergeCell ref="F10:F15"/>
     <mergeCell ref="Q4:Q9"/>
     <mergeCell ref="D28:D33"/>
@@ -6629,6 +6620,12 @@
     <mergeCell ref="P4:P9"/>
     <mergeCell ref="D10:D15"/>
     <mergeCell ref="E10:E15"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6639,25 +6636,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F504AC-2D47-497F-907C-E6D0C4842365}">
   <dimension ref="A1:Q51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -6678,11 +6675,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -6717,9 +6714,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="126">
         <v>46176</v>
@@ -6727,9 +6724,9 @@
       <c r="C4" s="46">
         <v>2</v>
       </c>
-      <c r="D4" s="250"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="256"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="263"/>
       <c r="G4" s="28" t="s">
         <v>0</v>
       </c>
@@ -6741,16 +6738,16 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="264"/>
       <c r="G5" s="23"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2"/>
@@ -6760,16 +6757,16 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="23"/>
       <c r="H6" s="15"/>
       <c r="I6" s="2"/>
@@ -6778,16 +6775,16 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="20" t="s">
         <v>7</v>
       </c>
@@ -6799,16 +6796,16 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
-      <c r="D8" s="251"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="19"/>
       <c r="H8" s="15"/>
       <c r="I8" s="2"/>
@@ -6818,16 +6815,16 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="265"/>
       <c r="G9" s="19" t="s">
         <v>1</v>
       </c>
@@ -6839,12 +6836,12 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="132" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="129">
         <v>46179</v>
@@ -6852,9 +6849,9 @@
       <c r="C10" s="46">
         <v>2</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -6869,7 +6866,7 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="127">
         <v>46180</v>
@@ -6877,9 +6874,9 @@
       <c r="C11" s="48">
         <v>2</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -6892,13 +6889,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -6910,13 +6907,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -6931,13 +6928,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -6950,13 +6947,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -6971,9 +6968,9 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="53">
         <v>46180</v>
@@ -6981,9 +6978,9 @@
       <c r="C16" s="46">
         <v>8</v>
       </c>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -6995,16 +6992,16 @@
       <c r="M16" s="5"/>
       <c r="N16" s="8"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P16" s="250"/>
+      <c r="Q16" s="250"/>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -7014,16 +7011,16 @@
       <c r="M17" s="2"/>
       <c r="N17" s="9"/>
       <c r="O17" s="49"/>
-      <c r="P17" s="259"/>
-      <c r="Q17" s="259"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="251"/>
+      <c r="Q17" s="251"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -7033,16 +7030,16 @@
       <c r="M18" s="2"/>
       <c r="N18" s="9"/>
       <c r="O18" s="49"/>
-      <c r="P18" s="259"/>
-      <c r="Q18" s="259"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="251"/>
+      <c r="Q18" s="251"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -7054,16 +7051,16 @@
       <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="62"/>
-      <c r="P19" s="259"/>
-      <c r="Q19" s="259"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="251"/>
+      <c r="Q19" s="251"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -7073,16 +7070,16 @@
       <c r="M20" s="2"/>
       <c r="N20" s="9"/>
       <c r="O20" s="49"/>
-      <c r="P20" s="259"/>
-      <c r="Q20" s="259"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="251"/>
+      <c r="Q20" s="251"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -7094,10 +7091,10 @@
       <c r="M21" s="6"/>
       <c r="N21" s="10"/>
       <c r="O21" s="51"/>
-      <c r="P21" s="265"/>
-      <c r="Q21" s="265"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="252"/>
+      <c r="Q21" s="252"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>23</v>
       </c>
@@ -7107,9 +7104,9 @@
       <c r="C22" s="46">
         <v>10</v>
       </c>
-      <c r="D22" s="250"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="22" t="s">
         <v>0</v>
       </c>
@@ -7121,10 +7118,10 @@
       <c r="M22" s="5"/>
       <c r="N22" s="8"/>
       <c r="O22" s="47"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="250"/>
+      <c r="Q22" s="250"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="127">
         <v>46187</v>
@@ -7132,9 +7129,9 @@
       <c r="C23" s="48">
         <v>5</v>
       </c>
-      <c r="D23" s="251"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="257"/>
+      <c r="D23" s="258"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="264"/>
       <c r="G23" s="23"/>
       <c r="H23" s="15"/>
       <c r="I23" s="2"/>
@@ -7144,16 +7141,16 @@
       <c r="M23" s="2"/>
       <c r="N23" s="9"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="263"/>
-      <c r="Q23" s="263"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="255"/>
+      <c r="Q23" s="255"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="264"/>
       <c r="G24" s="23"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2"/>
@@ -7163,16 +7160,16 @@
       <c r="M24" s="2"/>
       <c r="N24" s="9"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="263"/>
-      <c r="Q24" s="263"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="255"/>
+      <c r="Q24" s="255"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="257"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="264"/>
       <c r="G25" s="20" t="s">
         <v>7</v>
       </c>
@@ -7184,16 +7181,16 @@
       <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="62"/>
-      <c r="P25" s="263"/>
-      <c r="Q25" s="263"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="255"/>
+      <c r="Q25" s="255"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="251"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="257"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="264"/>
       <c r="G26" s="19"/>
       <c r="H26" s="15"/>
       <c r="I26" s="2"/>
@@ -7203,16 +7200,16 @@
       <c r="M26" s="2"/>
       <c r="N26" s="9"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="263"/>
-      <c r="Q26" s="263"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="255"/>
+      <c r="Q26" s="255"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="265"/>
       <c r="G27" s="19" t="s">
         <v>1</v>
       </c>
@@ -7224,10 +7221,10 @@
       <c r="M27" s="6"/>
       <c r="N27" s="10"/>
       <c r="O27" s="51"/>
-      <c r="P27" s="264"/>
-      <c r="Q27" s="264"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40" t="s">
         <v>24</v>
       </c>
@@ -7237,9 +7234,9 @@
       <c r="C28" s="46">
         <v>20</v>
       </c>
-      <c r="D28" s="250"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="256"/>
+      <c r="D28" s="257"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="263"/>
       <c r="G28" s="22" t="s">
         <v>0</v>
       </c>
@@ -7251,16 +7248,16 @@
       <c r="M28" s="5"/>
       <c r="N28" s="8"/>
       <c r="O28" s="47"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="250"/>
+      <c r="Q28" s="250"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="254"/>
-      <c r="F29" s="257"/>
+      <c r="D29" s="258"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="264"/>
       <c r="G29" s="23"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -7270,16 +7267,16 @@
       <c r="M29" s="2"/>
       <c r="N29" s="9"/>
       <c r="O29" s="49"/>
-      <c r="P29" s="259"/>
-      <c r="Q29" s="259"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="254"/>
-      <c r="F30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="261"/>
+      <c r="F30" s="264"/>
       <c r="G30" s="23"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -7289,16 +7286,16 @@
       <c r="M30" s="2"/>
       <c r="N30" s="9"/>
       <c r="O30" s="49"/>
-      <c r="P30" s="259"/>
-      <c r="Q30" s="259"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="261"/>
+      <c r="F31" s="264"/>
       <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
@@ -7310,16 +7307,16 @@
       <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="62"/>
-      <c r="P31" s="259"/>
-      <c r="Q31" s="259"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="251"/>
+      <c r="Q31" s="251"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
-      <c r="D32" s="251"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="264"/>
       <c r="G32" s="19"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -7329,16 +7326,16 @@
       <c r="M32" s="2"/>
       <c r="N32" s="9"/>
       <c r="O32" s="49"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="251"/>
+      <c r="Q32" s="251"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="265"/>
       <c r="G33" s="19" t="s">
         <v>1</v>
       </c>
@@ -7350,16 +7347,16 @@
       <c r="M33" s="6"/>
       <c r="N33" s="10"/>
       <c r="O33" s="51"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="265"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="53"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="256"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="263"/>
       <c r="G34" s="22" t="s">
         <v>0</v>
       </c>
@@ -7371,16 +7368,16 @@
       <c r="M34" s="5"/>
       <c r="N34" s="8"/>
       <c r="O34" s="47"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="250"/>
+      <c r="Q34" s="250"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="258"/>
+      <c r="E35" s="261"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="23"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -7390,16 +7387,16 @@
       <c r="M35" s="2"/>
       <c r="N35" s="9"/>
       <c r="O35" s="49"/>
-      <c r="P35" s="259"/>
-      <c r="Q35" s="259"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="251"/>
+      <c r="Q35" s="251"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="257"/>
+      <c r="D36" s="258"/>
+      <c r="E36" s="261"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="23"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -7409,16 +7406,16 @@
       <c r="M36" s="2"/>
       <c r="N36" s="9"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="251"/>
+      <c r="Q36" s="251"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
-      <c r="D37" s="251"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="257"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="261"/>
+      <c r="F37" s="264"/>
       <c r="G37" s="20" t="s">
         <v>7</v>
       </c>
@@ -7430,16 +7427,16 @@
       <c r="M37" s="25"/>
       <c r="N37" s="26"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="251"/>
+      <c r="Q37" s="251"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="251"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="257"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="261"/>
+      <c r="F38" s="264"/>
       <c r="G38" s="19"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -7449,16 +7446,16 @@
       <c r="M38" s="2"/>
       <c r="N38" s="9"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="251"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="258"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="265"/>
       <c r="G39" s="19" t="s">
         <v>1</v>
       </c>
@@ -7470,16 +7467,16 @@
       <c r="M39" s="6"/>
       <c r="N39" s="10"/>
       <c r="O39" s="51"/>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="265"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="252"/>
+      <c r="Q39" s="252"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="256"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="263"/>
       <c r="G40" s="22" t="s">
         <v>0</v>
       </c>
@@ -7491,16 +7488,16 @@
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="47"/>
-      <c r="P40" s="262"/>
-      <c r="Q40" s="262"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="257"/>
+      <c r="D41" s="258"/>
+      <c r="E41" s="261"/>
+      <c r="F41" s="264"/>
       <c r="G41" s="23"/>
       <c r="H41" s="15"/>
       <c r="I41" s="2"/>
@@ -7510,16 +7507,16 @@
       <c r="M41" s="2"/>
       <c r="N41" s="9"/>
       <c r="O41" s="49"/>
-      <c r="P41" s="259"/>
-      <c r="Q41" s="259"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="251"/>
+      <c r="Q41" s="251"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="257"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="264"/>
       <c r="G42" s="23"/>
       <c r="H42" s="15"/>
       <c r="I42" s="2"/>
@@ -7529,16 +7526,16 @@
       <c r="M42" s="2"/>
       <c r="N42" s="9"/>
       <c r="O42" s="49"/>
-      <c r="P42" s="259"/>
-      <c r="Q42" s="259"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="251"/>
+      <c r="Q42" s="251"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="251"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="257"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="261"/>
+      <c r="F43" s="264"/>
       <c r="G43" s="20" t="s">
         <v>7</v>
       </c>
@@ -7550,16 +7547,16 @@
       <c r="M43" s="25"/>
       <c r="N43" s="26"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="259"/>
-      <c r="Q43" s="259"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="251"/>
+      <c r="Q43" s="251"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="251"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="257"/>
+      <c r="D44" s="258"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="264"/>
       <c r="G44" s="19"/>
       <c r="H44" s="15"/>
       <c r="I44" s="2"/>
@@ -7569,16 +7566,16 @@
       <c r="M44" s="2"/>
       <c r="N44" s="9"/>
       <c r="O44" s="49"/>
-      <c r="P44" s="259"/>
-      <c r="Q44" s="259"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="251"/>
+      <c r="Q44" s="251"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="252"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="258"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="265"/>
       <c r="G45" s="19" t="s">
         <v>1</v>
       </c>
@@ -7590,16 +7587,16 @@
       <c r="M45" s="6"/>
       <c r="N45" s="10"/>
       <c r="O45" s="51"/>
-      <c r="P45" s="265"/>
-      <c r="Q45" s="265"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="252"/>
+      <c r="Q45" s="252"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="253"/>
-      <c r="F46" s="256"/>
+      <c r="D46" s="257"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="263"/>
       <c r="G46" s="22" t="s">
         <v>0</v>
       </c>
@@ -7611,16 +7608,16 @@
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="47"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="262"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="250"/>
+      <c r="Q46" s="250"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
-      <c r="D47" s="251"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="257"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="261"/>
+      <c r="F47" s="264"/>
       <c r="G47" s="23"/>
       <c r="H47" s="15"/>
       <c r="I47" s="2"/>
@@ -7630,16 +7627,16 @@
       <c r="M47" s="2"/>
       <c r="N47" s="9"/>
       <c r="O47" s="49"/>
-      <c r="P47" s="259"/>
-      <c r="Q47" s="259"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="251"/>
+      <c r="Q47" s="251"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
-      <c r="D48" s="251"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="257"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="261"/>
+      <c r="F48" s="264"/>
       <c r="G48" s="23"/>
       <c r="H48" s="15"/>
       <c r="I48" s="2"/>
@@ -7649,16 +7646,16 @@
       <c r="M48" s="2"/>
       <c r="N48" s="9"/>
       <c r="O48" s="49"/>
-      <c r="P48" s="259"/>
-      <c r="Q48" s="259"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="251"/>
+      <c r="Q48" s="251"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="257"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="261"/>
+      <c r="F49" s="264"/>
       <c r="G49" s="20" t="s">
         <v>7</v>
       </c>
@@ -7670,16 +7667,16 @@
       <c r="M49" s="25"/>
       <c r="N49" s="26"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="259"/>
-      <c r="Q49" s="259"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P49" s="251"/>
+      <c r="Q49" s="251"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="257"/>
+      <c r="D50" s="258"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="264"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
       <c r="I50" s="4"/>
@@ -7689,16 +7686,16 @@
       <c r="M50" s="4"/>
       <c r="N50" s="11"/>
       <c r="O50" s="52"/>
-      <c r="P50" s="259"/>
-      <c r="Q50" s="259"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="251"/>
+      <c r="Q50" s="251"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
-      <c r="D51" s="252"/>
-      <c r="E51" s="255"/>
-      <c r="F51" s="258"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="265"/>
       <c r="G51" s="21" t="s">
         <v>1</v>
       </c>
@@ -7710,18 +7707,34 @@
       <c r="M51" s="6"/>
       <c r="N51" s="10"/>
       <c r="O51" s="51"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="265"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="Q40:Q45"/>
-    <mergeCell ref="Q46:Q51"/>
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="Q16:Q21"/>
-    <mergeCell ref="Q22:Q27"/>
-    <mergeCell ref="Q28:Q33"/>
-    <mergeCell ref="Q34:Q39"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="P28:P33"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="P34:P39"/>
     <mergeCell ref="D40:D45"/>
     <mergeCell ref="E40:E45"/>
     <mergeCell ref="F40:F45"/>
@@ -7730,29 +7743,13 @@
     <mergeCell ref="E46:E51"/>
     <mergeCell ref="F46:F51"/>
     <mergeCell ref="P46:P51"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="P34:P39"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="P16:P21"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="P22:P27"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="Q40:Q45"/>
+    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="Q16:Q21"/>
+    <mergeCell ref="Q22:Q27"/>
+    <mergeCell ref="Q28:Q33"/>
+    <mergeCell ref="Q34:Q39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7762,25 +7759,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8803A0-19AD-4870-B4D0-09EB0BA11C3D}">
   <dimension ref="A1:T51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -7801,11 +7798,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -7840,7 +7837,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="45"/>
       <c r="C4" s="46"/>
@@ -7858,12 +7855,12 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="127">
         <v>46208</v>
@@ -7883,10 +7880,10 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="127"/>
       <c r="C6" s="48"/>
@@ -7901,10 +7898,10 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="127"/>
       <c r="C7" s="48"/>
@@ -7922,10 +7919,10 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
@@ -7941,10 +7938,10 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
@@ -7962,18 +7959,18 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="137" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="53"/>
       <c r="C10" s="46"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -7988,15 +7985,15 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="149" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -8009,13 +8006,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -8027,13 +8024,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -8048,13 +8045,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -8067,13 +8064,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -8088,19 +8085,19 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="53" t="s">
-        <v>37</v>
+      <c r="B16" s="53">
+        <v>46221</v>
       </c>
       <c r="C16" s="46">
         <v>14</v>
       </c>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -8112,17 +8109,17 @@
       <c r="M16" s="5"/>
       <c r="N16" s="8"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
+      <c r="P16" s="250"/>
+      <c r="Q16" s="250"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -8132,16 +8129,16 @@
       <c r="M17" s="2"/>
       <c r="N17" s="9"/>
       <c r="O17" s="49"/>
-      <c r="P17" s="263"/>
-      <c r="Q17" s="263"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="255"/>
+      <c r="Q17" s="255"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -8151,16 +8148,16 @@
       <c r="M18" s="2"/>
       <c r="N18" s="9"/>
       <c r="O18" s="49"/>
-      <c r="P18" s="263"/>
-      <c r="Q18" s="263"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="255"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -8172,16 +8169,16 @@
       <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="62"/>
-      <c r="P19" s="263"/>
-      <c r="Q19" s="263"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="255"/>
+      <c r="Q19" s="255"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -8191,16 +8188,16 @@
       <c r="M20" s="2"/>
       <c r="N20" s="9"/>
       <c r="O20" s="49"/>
-      <c r="P20" s="263"/>
-      <c r="Q20" s="263"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="255"/>
+      <c r="Q20" s="255"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -8212,10 +8209,10 @@
       <c r="M21" s="6"/>
       <c r="N21" s="10"/>
       <c r="O21" s="51"/>
-      <c r="P21" s="264"/>
-      <c r="Q21" s="264"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="256"/>
+      <c r="Q21" s="256"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>26</v>
       </c>
@@ -8225,9 +8222,9 @@
       <c r="C22" s="46">
         <v>20</v>
       </c>
-      <c r="D22" s="250"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="22" t="s">
         <v>0</v>
       </c>
@@ -8239,16 +8236,16 @@
       <c r="M22" s="5"/>
       <c r="N22" s="8"/>
       <c r="O22" s="47"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="250"/>
+      <c r="Q22" s="250"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="257"/>
+      <c r="D23" s="258"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="264"/>
       <c r="G23" s="23"/>
       <c r="H23" s="15"/>
       <c r="I23" s="2"/>
@@ -8258,16 +8255,16 @@
       <c r="M23" s="2"/>
       <c r="N23" s="9"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="263"/>
-      <c r="Q23" s="263"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="255"/>
+      <c r="Q23" s="255"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="264"/>
       <c r="G24" s="23"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2"/>
@@ -8277,16 +8274,16 @@
       <c r="M24" s="2"/>
       <c r="N24" s="9"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="263"/>
-      <c r="Q24" s="263"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="255"/>
+      <c r="Q24" s="255"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="257"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="264"/>
       <c r="G25" s="20" t="s">
         <v>7</v>
       </c>
@@ -8298,16 +8295,16 @@
       <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="62"/>
-      <c r="P25" s="263"/>
-      <c r="Q25" s="263"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="255"/>
+      <c r="Q25" s="255"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="251"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="257"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="264"/>
       <c r="G26" s="19"/>
       <c r="H26" s="15"/>
       <c r="I26" s="2"/>
@@ -8317,16 +8314,16 @@
       <c r="M26" s="2"/>
       <c r="N26" s="9"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="263"/>
-      <c r="Q26" s="263"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="255"/>
+      <c r="Q26" s="255"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="265"/>
       <c r="G27" s="19" t="s">
         <v>1</v>
       </c>
@@ -8338,16 +8335,16 @@
       <c r="M27" s="6"/>
       <c r="N27" s="10"/>
       <c r="O27" s="51"/>
-      <c r="P27" s="264"/>
-      <c r="Q27" s="264"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
       <c r="B28" s="53"/>
       <c r="C28" s="46"/>
-      <c r="D28" s="250"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="256"/>
+      <c r="D28" s="257"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="263"/>
       <c r="G28" s="22" t="s">
         <v>0</v>
       </c>
@@ -8359,16 +8356,16 @@
       <c r="M28" s="5"/>
       <c r="N28" s="8"/>
       <c r="O28" s="47"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="250"/>
+      <c r="Q28" s="250"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="254"/>
-      <c r="F29" s="257"/>
+      <c r="D29" s="258"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="264"/>
       <c r="G29" s="23"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -8378,16 +8375,16 @@
       <c r="M29" s="2"/>
       <c r="N29" s="9"/>
       <c r="O29" s="49"/>
-      <c r="P29" s="259"/>
-      <c r="Q29" s="259"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="254"/>
-      <c r="F30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="261"/>
+      <c r="F30" s="264"/>
       <c r="G30" s="23"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -8397,16 +8394,16 @@
       <c r="M30" s="2"/>
       <c r="N30" s="9"/>
       <c r="O30" s="49"/>
-      <c r="P30" s="259"/>
-      <c r="Q30" s="259"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="261"/>
+      <c r="F31" s="264"/>
       <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
@@ -8418,16 +8415,16 @@
       <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="62"/>
-      <c r="P31" s="259"/>
-      <c r="Q31" s="259"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="251"/>
+      <c r="Q31" s="251"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
-      <c r="D32" s="251"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="264"/>
       <c r="G32" s="19"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -8437,16 +8434,16 @@
       <c r="M32" s="2"/>
       <c r="N32" s="9"/>
       <c r="O32" s="49"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="251"/>
+      <c r="Q32" s="251"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="265"/>
       <c r="G33" s="19" t="s">
         <v>1</v>
       </c>
@@ -8458,16 +8455,16 @@
       <c r="M33" s="6"/>
       <c r="N33" s="10"/>
       <c r="O33" s="51"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="265"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="53"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="256"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="263"/>
       <c r="G34" s="22" t="s">
         <v>0</v>
       </c>
@@ -8479,16 +8476,16 @@
       <c r="M34" s="5"/>
       <c r="N34" s="8"/>
       <c r="O34" s="47"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="250"/>
+      <c r="Q34" s="250"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="258"/>
+      <c r="E35" s="261"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="23"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -8498,16 +8495,16 @@
       <c r="M35" s="2"/>
       <c r="N35" s="9"/>
       <c r="O35" s="49"/>
-      <c r="P35" s="259"/>
-      <c r="Q35" s="259"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="251"/>
+      <c r="Q35" s="251"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="257"/>
+      <c r="D36" s="258"/>
+      <c r="E36" s="261"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="23"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -8517,16 +8514,16 @@
       <c r="M36" s="2"/>
       <c r="N36" s="9"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="251"/>
+      <c r="Q36" s="251"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
-      <c r="D37" s="251"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="257"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="261"/>
+      <c r="F37" s="264"/>
       <c r="G37" s="20" t="s">
         <v>7</v>
       </c>
@@ -8538,16 +8535,16 @@
       <c r="M37" s="25"/>
       <c r="N37" s="26"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="251"/>
+      <c r="Q37" s="251"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="251"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="257"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="261"/>
+      <c r="F38" s="264"/>
       <c r="G38" s="19"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -8557,16 +8554,16 @@
       <c r="M38" s="2"/>
       <c r="N38" s="9"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="251"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="258"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="265"/>
       <c r="G39" s="19" t="s">
         <v>1</v>
       </c>
@@ -8578,16 +8575,16 @@
       <c r="M39" s="6"/>
       <c r="N39" s="10"/>
       <c r="O39" s="51"/>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="265"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="252"/>
+      <c r="Q39" s="252"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="256"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="263"/>
       <c r="G40" s="22" t="s">
         <v>0</v>
       </c>
@@ -8599,16 +8596,16 @@
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="47"/>
-      <c r="P40" s="262"/>
-      <c r="Q40" s="262"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="257"/>
+      <c r="D41" s="258"/>
+      <c r="E41" s="261"/>
+      <c r="F41" s="264"/>
       <c r="G41" s="23"/>
       <c r="H41" s="15"/>
       <c r="I41" s="2"/>
@@ -8618,16 +8615,16 @@
       <c r="M41" s="2"/>
       <c r="N41" s="9"/>
       <c r="O41" s="49"/>
-      <c r="P41" s="259"/>
-      <c r="Q41" s="259"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="251"/>
+      <c r="Q41" s="251"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="257"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="264"/>
       <c r="G42" s="23"/>
       <c r="H42" s="15"/>
       <c r="I42" s="2"/>
@@ -8637,16 +8634,16 @@
       <c r="M42" s="2"/>
       <c r="N42" s="9"/>
       <c r="O42" s="49"/>
-      <c r="P42" s="259"/>
-      <c r="Q42" s="259"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="251"/>
+      <c r="Q42" s="251"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="251"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="257"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="261"/>
+      <c r="F43" s="264"/>
       <c r="G43" s="20" t="s">
         <v>7</v>
       </c>
@@ -8658,16 +8655,16 @@
       <c r="M43" s="25"/>
       <c r="N43" s="26"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="259"/>
-      <c r="Q43" s="259"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="251"/>
+      <c r="Q43" s="251"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="251"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="257"/>
+      <c r="D44" s="258"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="264"/>
       <c r="G44" s="19"/>
       <c r="H44" s="15"/>
       <c r="I44" s="2"/>
@@ -8677,16 +8674,16 @@
       <c r="M44" s="2"/>
       <c r="N44" s="9"/>
       <c r="O44" s="49"/>
-      <c r="P44" s="259"/>
-      <c r="Q44" s="259"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="251"/>
+      <c r="Q44" s="251"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="252"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="258"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="265"/>
       <c r="G45" s="19" t="s">
         <v>1</v>
       </c>
@@ -8698,16 +8695,16 @@
       <c r="M45" s="6"/>
       <c r="N45" s="10"/>
       <c r="O45" s="51"/>
-      <c r="P45" s="265"/>
-      <c r="Q45" s="265"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="252"/>
+      <c r="Q45" s="252"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="253"/>
-      <c r="F46" s="256"/>
+      <c r="D46" s="257"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="263"/>
       <c r="G46" s="22" t="s">
         <v>0</v>
       </c>
@@ -8719,16 +8716,16 @@
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="47"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="262"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="250"/>
+      <c r="Q46" s="250"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
-      <c r="D47" s="251"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="257"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="261"/>
+      <c r="F47" s="264"/>
       <c r="G47" s="23"/>
       <c r="H47" s="15"/>
       <c r="I47" s="2"/>
@@ -8738,16 +8735,16 @@
       <c r="M47" s="2"/>
       <c r="N47" s="9"/>
       <c r="O47" s="49"/>
-      <c r="P47" s="259"/>
-      <c r="Q47" s="259"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="251"/>
+      <c r="Q47" s="251"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
-      <c r="D48" s="251"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="257"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="261"/>
+      <c r="F48" s="264"/>
       <c r="G48" s="23"/>
       <c r="H48" s="15"/>
       <c r="I48" s="2"/>
@@ -8757,16 +8754,16 @@
       <c r="M48" s="2"/>
       <c r="N48" s="9"/>
       <c r="O48" s="49"/>
-      <c r="P48" s="259"/>
-      <c r="Q48" s="259"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="251"/>
+      <c r="Q48" s="251"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="257"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="261"/>
+      <c r="F49" s="264"/>
       <c r="G49" s="20" t="s">
         <v>7</v>
       </c>
@@ -8778,16 +8775,16 @@
       <c r="M49" s="25"/>
       <c r="N49" s="26"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="259"/>
-      <c r="Q49" s="259"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P49" s="251"/>
+      <c r="Q49" s="251"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="257"/>
+      <c r="D50" s="258"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="264"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
       <c r="I50" s="4"/>
@@ -8797,16 +8794,16 @@
       <c r="M50" s="4"/>
       <c r="N50" s="11"/>
       <c r="O50" s="52"/>
-      <c r="P50" s="259"/>
-      <c r="Q50" s="259"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="251"/>
+      <c r="Q50" s="251"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
-      <c r="D51" s="252"/>
-      <c r="E51" s="255"/>
-      <c r="F51" s="258"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="265"/>
       <c r="G51" s="21" t="s">
         <v>1</v>
       </c>
@@ -8818,22 +8815,27 @@
       <c r="M51" s="6"/>
       <c r="N51" s="10"/>
       <c r="O51" s="51"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="265"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="Q16:Q21"/>
-    <mergeCell ref="Q22:Q27"/>
-    <mergeCell ref="Q28:Q33"/>
-    <mergeCell ref="Q34:Q39"/>
-    <mergeCell ref="D46:D51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="P46:P51"/>
-    <mergeCell ref="Q40:Q45"/>
-    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="P28:P33"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="E34:E39"/>
     <mergeCell ref="F34:F39"/>
@@ -8842,22 +8844,17 @@
     <mergeCell ref="E40:E45"/>
     <mergeCell ref="F40:F45"/>
     <mergeCell ref="P40:P45"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="P22:P27"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D46:D51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="P46:P51"/>
+    <mergeCell ref="Q40:Q45"/>
+    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="Q16:Q21"/>
+    <mergeCell ref="Q22:Q27"/>
+    <mergeCell ref="Q28:Q33"/>
+    <mergeCell ref="Q34:Q39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -8867,25 +8864,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22FAF75-32EA-465F-9FBF-3F59B0CA4D78}">
   <dimension ref="A1:T51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -8906,11 +8903,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -8945,9 +8942,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="126">
         <v>46238</v>
@@ -8955,9 +8952,9 @@
       <c r="C4" s="46">
         <v>4</v>
       </c>
-      <c r="D4" s="250"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="256"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="263"/>
       <c r="G4" s="28" t="s">
         <v>0</v>
       </c>
@@ -8969,16 +8966,16 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="264"/>
       <c r="G5" s="23"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2"/>
@@ -8988,16 +8985,16 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="23"/>
       <c r="H6" s="15"/>
       <c r="I6" s="2"/>
@@ -9006,16 +9003,16 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="20" t="s">
         <v>7</v>
       </c>
@@ -9027,16 +9024,16 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
-      <c r="D8" s="251"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="19"/>
       <c r="H8" s="15"/>
       <c r="I8" s="2"/>
@@ -9046,16 +9043,16 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="265"/>
       <c r="G9" s="19" t="s">
         <v>1</v>
       </c>
@@ -9067,10 +9064,10 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>34</v>
       </c>
@@ -9080,9 +9077,9 @@
       <c r="C10" s="46">
         <v>6</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -9097,13 +9094,13 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -9116,13 +9113,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -9134,13 +9131,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -9155,13 +9152,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -9174,13 +9171,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -9195,7 +9192,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="137" t="s">
         <v>29</v>
       </c>
@@ -9203,9 +9200,9 @@
         <v>30</v>
       </c>
       <c r="C16" s="46"/>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -9217,21 +9214,21 @@
       <c r="M16" s="5"/>
       <c r="N16" s="8"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
+      <c r="P16" s="250"/>
+      <c r="Q16" s="250"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="149" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="131" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -9241,18 +9238,18 @@
       <c r="M17" s="2"/>
       <c r="N17" s="9"/>
       <c r="O17" s="49"/>
-      <c r="P17" s="263"/>
-      <c r="Q17" s="263"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="255"/>
+      <c r="Q17" s="255"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="127" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="130"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -9262,18 +9259,18 @@
       <c r="M18" s="2"/>
       <c r="N18" s="9"/>
       <c r="O18" s="49"/>
-      <c r="P18" s="263"/>
-      <c r="Q18" s="263"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="255"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="128" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -9285,16 +9282,16 @@
       <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="62"/>
-      <c r="P19" s="263"/>
-      <c r="Q19" s="263"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="255"/>
+      <c r="Q19" s="255"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -9304,16 +9301,16 @@
       <c r="M20" s="2"/>
       <c r="N20" s="9"/>
       <c r="O20" s="49"/>
-      <c r="P20" s="263"/>
-      <c r="Q20" s="263"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="255"/>
+      <c r="Q20" s="255"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -9325,10 +9322,10 @@
       <c r="M21" s="6"/>
       <c r="N21" s="10"/>
       <c r="O21" s="51"/>
-      <c r="P21" s="264"/>
-      <c r="Q21" s="264"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="256"/>
+      <c r="Q21" s="256"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>27</v>
       </c>
@@ -9338,9 +9335,9 @@
       <c r="C22" s="46">
         <v>8</v>
       </c>
-      <c r="D22" s="250"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="22" t="s">
         <v>0</v>
       </c>
@@ -9352,16 +9349,16 @@
       <c r="M22" s="5"/>
       <c r="N22" s="8"/>
       <c r="O22" s="47"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="250"/>
+      <c r="Q22" s="250"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="257"/>
+      <c r="D23" s="258"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="264"/>
       <c r="G23" s="23"/>
       <c r="H23" s="15"/>
       <c r="I23" s="2"/>
@@ -9371,16 +9368,16 @@
       <c r="M23" s="2"/>
       <c r="N23" s="9"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="263"/>
-      <c r="Q23" s="263"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="255"/>
+      <c r="Q23" s="255"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="264"/>
       <c r="G24" s="23"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2"/>
@@ -9390,16 +9387,16 @@
       <c r="M24" s="2"/>
       <c r="N24" s="9"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="263"/>
-      <c r="Q24" s="263"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="255"/>
+      <c r="Q24" s="255"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="257"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="264"/>
       <c r="G25" s="20" t="s">
         <v>7</v>
       </c>
@@ -9411,16 +9408,16 @@
       <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="62"/>
-      <c r="P25" s="263"/>
-      <c r="Q25" s="263"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="255"/>
+      <c r="Q25" s="255"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="251"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="257"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="264"/>
       <c r="G26" s="19"/>
       <c r="H26" s="15"/>
       <c r="I26" s="2"/>
@@ -9430,16 +9427,16 @@
       <c r="M26" s="2"/>
       <c r="N26" s="9"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="263"/>
-      <c r="Q26" s="263"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="255"/>
+      <c r="Q26" s="255"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="265"/>
       <c r="G27" s="19" t="s">
         <v>1</v>
       </c>
@@ -9451,16 +9448,16 @@
       <c r="M27" s="6"/>
       <c r="N27" s="10"/>
       <c r="O27" s="51"/>
-      <c r="P27" s="264"/>
-      <c r="Q27" s="264"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
       <c r="B28" s="53"/>
       <c r="C28" s="46"/>
-      <c r="D28" s="250"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="256"/>
+      <c r="D28" s="257"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="263"/>
       <c r="G28" s="22" t="s">
         <v>0</v>
       </c>
@@ -9472,16 +9469,16 @@
       <c r="M28" s="5"/>
       <c r="N28" s="8"/>
       <c r="O28" s="47"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="250"/>
+      <c r="Q28" s="250"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="254"/>
-      <c r="F29" s="257"/>
+      <c r="D29" s="258"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="264"/>
       <c r="G29" s="23"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -9491,16 +9488,16 @@
       <c r="M29" s="2"/>
       <c r="N29" s="9"/>
       <c r="O29" s="49"/>
-      <c r="P29" s="259"/>
-      <c r="Q29" s="259"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="254"/>
-      <c r="F30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="261"/>
+      <c r="F30" s="264"/>
       <c r="G30" s="23"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -9510,16 +9507,16 @@
       <c r="M30" s="2"/>
       <c r="N30" s="9"/>
       <c r="O30" s="49"/>
-      <c r="P30" s="259"/>
-      <c r="Q30" s="259"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="261"/>
+      <c r="F31" s="264"/>
       <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
@@ -9531,16 +9528,16 @@
       <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="62"/>
-      <c r="P31" s="259"/>
-      <c r="Q31" s="259"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="251"/>
+      <c r="Q31" s="251"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
-      <c r="D32" s="251"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="264"/>
       <c r="G32" s="19"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -9550,16 +9547,16 @@
       <c r="M32" s="2"/>
       <c r="N32" s="9"/>
       <c r="O32" s="49"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="251"/>
+      <c r="Q32" s="251"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="265"/>
       <c r="G33" s="19" t="s">
         <v>1</v>
       </c>
@@ -9571,16 +9568,16 @@
       <c r="M33" s="6"/>
       <c r="N33" s="10"/>
       <c r="O33" s="51"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="265"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="53"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="256"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="263"/>
       <c r="G34" s="22" t="s">
         <v>0</v>
       </c>
@@ -9592,16 +9589,16 @@
       <c r="M34" s="5"/>
       <c r="N34" s="8"/>
       <c r="O34" s="47"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="250"/>
+      <c r="Q34" s="250"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="258"/>
+      <c r="E35" s="261"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="23"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -9611,16 +9608,16 @@
       <c r="M35" s="2"/>
       <c r="N35" s="9"/>
       <c r="O35" s="49"/>
-      <c r="P35" s="259"/>
-      <c r="Q35" s="259"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="251"/>
+      <c r="Q35" s="251"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="257"/>
+      <c r="D36" s="258"/>
+      <c r="E36" s="261"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="23"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -9630,16 +9627,16 @@
       <c r="M36" s="2"/>
       <c r="N36" s="9"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="251"/>
+      <c r="Q36" s="251"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
-      <c r="D37" s="251"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="257"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="261"/>
+      <c r="F37" s="264"/>
       <c r="G37" s="20" t="s">
         <v>7</v>
       </c>
@@ -9651,16 +9648,16 @@
       <c r="M37" s="25"/>
       <c r="N37" s="26"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="251"/>
+      <c r="Q37" s="251"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="251"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="257"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="261"/>
+      <c r="F38" s="264"/>
       <c r="G38" s="19"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -9670,16 +9667,16 @@
       <c r="M38" s="2"/>
       <c r="N38" s="9"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="251"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="258"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="265"/>
       <c r="G39" s="19" t="s">
         <v>1</v>
       </c>
@@ -9691,16 +9688,16 @@
       <c r="M39" s="6"/>
       <c r="N39" s="10"/>
       <c r="O39" s="51"/>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="265"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="252"/>
+      <c r="Q39" s="252"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="256"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="263"/>
       <c r="G40" s="22" t="s">
         <v>0</v>
       </c>
@@ -9712,16 +9709,16 @@
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="47"/>
-      <c r="P40" s="262"/>
-      <c r="Q40" s="262"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="257"/>
+      <c r="D41" s="258"/>
+      <c r="E41" s="261"/>
+      <c r="F41" s="264"/>
       <c r="G41" s="23"/>
       <c r="H41" s="15"/>
       <c r="I41" s="2"/>
@@ -9731,16 +9728,16 @@
       <c r="M41" s="2"/>
       <c r="N41" s="9"/>
       <c r="O41" s="49"/>
-      <c r="P41" s="259"/>
-      <c r="Q41" s="259"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="251"/>
+      <c r="Q41" s="251"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="257"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="264"/>
       <c r="G42" s="23"/>
       <c r="H42" s="15"/>
       <c r="I42" s="2"/>
@@ -9750,16 +9747,16 @@
       <c r="M42" s="2"/>
       <c r="N42" s="9"/>
       <c r="O42" s="49"/>
-      <c r="P42" s="259"/>
-      <c r="Q42" s="259"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="251"/>
+      <c r="Q42" s="251"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="251"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="257"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="261"/>
+      <c r="F43" s="264"/>
       <c r="G43" s="20" t="s">
         <v>7</v>
       </c>
@@ -9771,16 +9768,16 @@
       <c r="M43" s="25"/>
       <c r="N43" s="26"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="259"/>
-      <c r="Q43" s="259"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="251"/>
+      <c r="Q43" s="251"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="251"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="257"/>
+      <c r="D44" s="258"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="264"/>
       <c r="G44" s="19"/>
       <c r="H44" s="15"/>
       <c r="I44" s="2"/>
@@ -9790,16 +9787,16 @@
       <c r="M44" s="2"/>
       <c r="N44" s="9"/>
       <c r="O44" s="49"/>
-      <c r="P44" s="259"/>
-      <c r="Q44" s="259"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="251"/>
+      <c r="Q44" s="251"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="252"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="258"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="265"/>
       <c r="G45" s="19" t="s">
         <v>1</v>
       </c>
@@ -9811,16 +9808,16 @@
       <c r="M45" s="6"/>
       <c r="N45" s="10"/>
       <c r="O45" s="51"/>
-      <c r="P45" s="265"/>
-      <c r="Q45" s="265"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="252"/>
+      <c r="Q45" s="252"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="253"/>
-      <c r="F46" s="256"/>
+      <c r="D46" s="257"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="263"/>
       <c r="G46" s="22" t="s">
         <v>0</v>
       </c>
@@ -9832,16 +9829,16 @@
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="47"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="262"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="250"/>
+      <c r="Q46" s="250"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
-      <c r="D47" s="251"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="257"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="261"/>
+      <c r="F47" s="264"/>
       <c r="G47" s="23"/>
       <c r="H47" s="15"/>
       <c r="I47" s="2"/>
@@ -9851,16 +9848,16 @@
       <c r="M47" s="2"/>
       <c r="N47" s="9"/>
       <c r="O47" s="49"/>
-      <c r="P47" s="259"/>
-      <c r="Q47" s="259"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="251"/>
+      <c r="Q47" s="251"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
-      <c r="D48" s="251"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="257"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="261"/>
+      <c r="F48" s="264"/>
       <c r="G48" s="23"/>
       <c r="H48" s="15"/>
       <c r="I48" s="2"/>
@@ -9870,16 +9867,16 @@
       <c r="M48" s="2"/>
       <c r="N48" s="9"/>
       <c r="O48" s="49"/>
-      <c r="P48" s="259"/>
-      <c r="Q48" s="259"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="251"/>
+      <c r="Q48" s="251"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="257"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="261"/>
+      <c r="F49" s="264"/>
       <c r="G49" s="20" t="s">
         <v>7</v>
       </c>
@@ -9891,16 +9888,16 @@
       <c r="M49" s="25"/>
       <c r="N49" s="26"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="259"/>
-      <c r="Q49" s="259"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P49" s="251"/>
+      <c r="Q49" s="251"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="257"/>
+      <c r="D50" s="258"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="264"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
       <c r="I50" s="4"/>
@@ -9910,16 +9907,16 @@
       <c r="M50" s="4"/>
       <c r="N50" s="11"/>
       <c r="O50" s="52"/>
-      <c r="P50" s="259"/>
-      <c r="Q50" s="259"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="251"/>
+      <c r="Q50" s="251"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
-      <c r="D51" s="252"/>
-      <c r="E51" s="255"/>
-      <c r="F51" s="258"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="265"/>
       <c r="G51" s="21" t="s">
         <v>1</v>
       </c>
@@ -9931,18 +9928,34 @@
       <c r="M51" s="6"/>
       <c r="N51" s="10"/>
       <c r="O51" s="51"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="265"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="Q40:Q45"/>
-    <mergeCell ref="Q46:Q51"/>
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="Q16:Q21"/>
-    <mergeCell ref="Q22:Q27"/>
-    <mergeCell ref="Q28:Q33"/>
-    <mergeCell ref="Q34:Q39"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="P28:P33"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="P34:P39"/>
     <mergeCell ref="D40:D45"/>
     <mergeCell ref="E40:E45"/>
     <mergeCell ref="F40:F45"/>
@@ -9951,29 +9964,13 @@
     <mergeCell ref="E46:E51"/>
     <mergeCell ref="F46:F51"/>
     <mergeCell ref="P46:P51"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="P34:P39"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="P16:P21"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="P22:P27"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="Q40:Q45"/>
+    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="Q16:Q21"/>
+    <mergeCell ref="Q22:Q27"/>
+    <mergeCell ref="Q28:Q33"/>
+    <mergeCell ref="Q34:Q39"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9984,25 +9981,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04BD2FE-01C2-4053-9BDB-335163CD9083}">
   <dimension ref="A1:T51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="11.453125" style="1"/>
-    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="1"/>
-    <col min="14" max="14" width="11.26953125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="56" t="s">
         <v>10</v>
       </c>
@@ -10023,11 +10020,11 @@
       <c r="P1" s="57"/>
       <c r="Q1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="55"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
         <v>3</v>
@@ -10062,9 +10059,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="126">
         <v>46278</v>
@@ -10072,9 +10069,9 @@
       <c r="C4" s="46">
         <v>8</v>
       </c>
-      <c r="D4" s="250"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="256"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="263"/>
       <c r="G4" s="28" t="s">
         <v>0</v>
       </c>
@@ -10086,16 +10083,16 @@
       <c r="M4" s="30"/>
       <c r="N4" s="27"/>
       <c r="O4" s="47"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="259"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="251"/>
+      <c r="Q4" s="251"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="264"/>
       <c r="G5" s="23"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2"/>
@@ -10105,16 +10102,16 @@
       <c r="M5" s="2"/>
       <c r="N5" s="9"/>
       <c r="O5" s="49"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="23"/>
       <c r="H6" s="15"/>
       <c r="I6" s="2"/>
@@ -10123,16 +10120,16 @@
       <c r="M6" s="2"/>
       <c r="N6" s="9"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="20" t="s">
         <v>7</v>
       </c>
@@ -10144,16 +10141,16 @@
       <c r="M7" s="12"/>
       <c r="N7" s="13"/>
       <c r="O7" s="62"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
-      <c r="D8" s="251"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="19"/>
       <c r="H8" s="15"/>
       <c r="I8" s="2"/>
@@ -10163,16 +10160,16 @@
       <c r="M8" s="2"/>
       <c r="N8" s="9"/>
       <c r="O8" s="49"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="253"/>
+      <c r="Q8" s="253"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="258"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="265"/>
       <c r="G9" s="19" t="s">
         <v>1</v>
       </c>
@@ -10184,16 +10181,16 @@
       <c r="M9" s="6"/>
       <c r="N9" s="10"/>
       <c r="O9" s="51"/>
-      <c r="P9" s="261"/>
-      <c r="Q9" s="261"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40"/>
       <c r="B10" s="53"/>
       <c r="C10" s="46"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="256"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="263"/>
       <c r="G10" s="22" t="s">
         <v>0</v>
       </c>
@@ -10208,9 +10205,9 @@
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="127">
         <v>46278</v>
@@ -10218,9 +10215,9 @@
       <c r="C11" s="48">
         <v>7</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="264"/>
       <c r="G11" s="23"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2"/>
@@ -10233,13 +10230,13 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="257"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="264"/>
       <c r="G12" s="23"/>
       <c r="H12" s="15"/>
       <c r="I12" s="2"/>
@@ -10251,13 +10248,13 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="257"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="264"/>
       <c r="G13" s="20" t="s">
         <v>7</v>
       </c>
@@ -10272,13 +10269,13 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="257"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="264"/>
       <c r="G14" s="19"/>
       <c r="H14" s="15"/>
       <c r="I14" s="2"/>
@@ -10291,13 +10288,13 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="265"/>
       <c r="G15" s="19" t="s">
         <v>1</v>
       </c>
@@ -10312,9 +10309,9 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="53">
         <v>46285</v>
@@ -10322,9 +10319,9 @@
       <c r="C16" s="46">
         <v>4</v>
       </c>
-      <c r="D16" s="250"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="263"/>
       <c r="G16" s="22" t="s">
         <v>0</v>
       </c>
@@ -10336,17 +10333,17 @@
       <c r="M16" s="5"/>
       <c r="N16" s="8"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
+      <c r="P16" s="250"/>
+      <c r="Q16" s="250"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="264"/>
       <c r="G17" s="23"/>
       <c r="H17" s="15"/>
       <c r="I17" s="2"/>
@@ -10356,16 +10353,16 @@
       <c r="M17" s="2"/>
       <c r="N17" s="9"/>
       <c r="O17" s="49"/>
-      <c r="P17" s="263"/>
-      <c r="Q17" s="263"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="255"/>
+      <c r="Q17" s="255"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="257"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="264"/>
       <c r="G18" s="23"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2"/>
@@ -10375,16 +10372,16 @@
       <c r="M18" s="2"/>
       <c r="N18" s="9"/>
       <c r="O18" s="49"/>
-      <c r="P18" s="263"/>
-      <c r="Q18" s="263"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="255"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="264"/>
       <c r="G19" s="20" t="s">
         <v>7</v>
       </c>
@@ -10396,16 +10393,16 @@
       <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="62"/>
-      <c r="P19" s="263"/>
-      <c r="Q19" s="263"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="255"/>
+      <c r="Q19" s="255"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="254"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="264"/>
       <c r="G20" s="19"/>
       <c r="H20" s="15"/>
       <c r="I20" s="2"/>
@@ -10415,16 +10412,16 @@
       <c r="M20" s="2"/>
       <c r="N20" s="9"/>
       <c r="O20" s="49"/>
-      <c r="P20" s="263"/>
-      <c r="Q20" s="263"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="255"/>
+      <c r="Q20" s="255"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="255"/>
-      <c r="F21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="265"/>
       <c r="G21" s="19" t="s">
         <v>1</v>
       </c>
@@ -10436,16 +10433,16 @@
       <c r="M21" s="6"/>
       <c r="N21" s="10"/>
       <c r="O21" s="51"/>
-      <c r="P21" s="264"/>
-      <c r="Q21" s="264"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="256"/>
+      <c r="Q21" s="256"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
       <c r="B22" s="53"/>
       <c r="C22" s="46"/>
-      <c r="D22" s="250"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="22" t="s">
         <v>0</v>
       </c>
@@ -10457,16 +10454,16 @@
       <c r="M22" s="5"/>
       <c r="N22" s="8"/>
       <c r="O22" s="47"/>
-      <c r="P22" s="262"/>
-      <c r="Q22" s="262"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="250"/>
+      <c r="Q22" s="250"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="257"/>
+      <c r="D23" s="258"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="264"/>
       <c r="G23" s="23"/>
       <c r="H23" s="15"/>
       <c r="I23" s="2"/>
@@ -10476,16 +10473,16 @@
       <c r="M23" s="2"/>
       <c r="N23" s="9"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="263"/>
-      <c r="Q23" s="263"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="255"/>
+      <c r="Q23" s="255"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="264"/>
       <c r="G24" s="23"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2"/>
@@ -10495,16 +10492,16 @@
       <c r="M24" s="2"/>
       <c r="N24" s="9"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="263"/>
-      <c r="Q24" s="263"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="255"/>
+      <c r="Q24" s="255"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="257"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="264"/>
       <c r="G25" s="20" t="s">
         <v>7</v>
       </c>
@@ -10516,16 +10513,16 @@
       <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="62"/>
-      <c r="P25" s="263"/>
-      <c r="Q25" s="263"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="255"/>
+      <c r="Q25" s="255"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="251"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="257"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="264"/>
       <c r="G26" s="19"/>
       <c r="H26" s="15"/>
       <c r="I26" s="2"/>
@@ -10535,16 +10532,16 @@
       <c r="M26" s="2"/>
       <c r="N26" s="9"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="263"/>
-      <c r="Q26" s="263"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="255"/>
+      <c r="Q26" s="255"/>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="265"/>
       <c r="G27" s="19" t="s">
         <v>1</v>
       </c>
@@ -10556,16 +10553,16 @@
       <c r="M27" s="6"/>
       <c r="N27" s="10"/>
       <c r="O27" s="51"/>
-      <c r="P27" s="264"/>
-      <c r="Q27" s="264"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
       <c r="B28" s="53"/>
       <c r="C28" s="46"/>
-      <c r="D28" s="250"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="256"/>
+      <c r="D28" s="257"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="263"/>
       <c r="G28" s="22" t="s">
         <v>0</v>
       </c>
@@ -10577,16 +10574,16 @@
       <c r="M28" s="5"/>
       <c r="N28" s="8"/>
       <c r="O28" s="47"/>
-      <c r="P28" s="262"/>
-      <c r="Q28" s="262"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="250"/>
+      <c r="Q28" s="250"/>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="254"/>
-      <c r="F29" s="257"/>
+      <c r="D29" s="258"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="264"/>
       <c r="G29" s="23"/>
       <c r="H29" s="15"/>
       <c r="I29" s="2"/>
@@ -10596,16 +10593,16 @@
       <c r="M29" s="2"/>
       <c r="N29" s="9"/>
       <c r="O29" s="49"/>
-      <c r="P29" s="259"/>
-      <c r="Q29" s="259"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="254"/>
-      <c r="F30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="261"/>
+      <c r="F30" s="264"/>
       <c r="G30" s="23"/>
       <c r="H30" s="15"/>
       <c r="I30" s="2"/>
@@ -10615,16 +10612,16 @@
       <c r="M30" s="2"/>
       <c r="N30" s="9"/>
       <c r="O30" s="49"/>
-      <c r="P30" s="259"/>
-      <c r="Q30" s="259"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="257"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="261"/>
+      <c r="F31" s="264"/>
       <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
@@ -10636,16 +10633,16 @@
       <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="62"/>
-      <c r="P31" s="259"/>
-      <c r="Q31" s="259"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="251"/>
+      <c r="Q31" s="251"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
-      <c r="D32" s="251"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="264"/>
       <c r="G32" s="19"/>
       <c r="H32" s="15"/>
       <c r="I32" s="2"/>
@@ -10655,16 +10652,16 @@
       <c r="M32" s="2"/>
       <c r="N32" s="9"/>
       <c r="O32" s="49"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="251"/>
+      <c r="Q32" s="251"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="265"/>
       <c r="G33" s="19" t="s">
         <v>1</v>
       </c>
@@ -10676,16 +10673,16 @@
       <c r="M33" s="6"/>
       <c r="N33" s="10"/>
       <c r="O33" s="51"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="265"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="53"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="256"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="263"/>
       <c r="G34" s="22" t="s">
         <v>0</v>
       </c>
@@ -10697,16 +10694,16 @@
       <c r="M34" s="5"/>
       <c r="N34" s="8"/>
       <c r="O34" s="47"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="250"/>
+      <c r="Q34" s="250"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="258"/>
+      <c r="E35" s="261"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="23"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2"/>
@@ -10716,16 +10713,16 @@
       <c r="M35" s="2"/>
       <c r="N35" s="9"/>
       <c r="O35" s="49"/>
-      <c r="P35" s="259"/>
-      <c r="Q35" s="259"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="251"/>
+      <c r="Q35" s="251"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="257"/>
+      <c r="D36" s="258"/>
+      <c r="E36" s="261"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="23"/>
       <c r="H36" s="15"/>
       <c r="I36" s="2"/>
@@ -10735,16 +10732,16 @@
       <c r="M36" s="2"/>
       <c r="N36" s="9"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="251"/>
+      <c r="Q36" s="251"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
-      <c r="D37" s="251"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="257"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="261"/>
+      <c r="F37" s="264"/>
       <c r="G37" s="20" t="s">
         <v>7</v>
       </c>
@@ -10756,16 +10753,16 @@
       <c r="M37" s="25"/>
       <c r="N37" s="26"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="251"/>
+      <c r="Q37" s="251"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="251"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="257"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="261"/>
+      <c r="F38" s="264"/>
       <c r="G38" s="19"/>
       <c r="H38" s="15"/>
       <c r="I38" s="2"/>
@@ -10775,16 +10772,16 @@
       <c r="M38" s="2"/>
       <c r="N38" s="9"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="251"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="258"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="265"/>
       <c r="G39" s="19" t="s">
         <v>1</v>
       </c>
@@ -10796,16 +10793,16 @@
       <c r="M39" s="6"/>
       <c r="N39" s="10"/>
       <c r="O39" s="51"/>
-      <c r="P39" s="265"/>
-      <c r="Q39" s="265"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="252"/>
+      <c r="Q39" s="252"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="256"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="263"/>
       <c r="G40" s="22" t="s">
         <v>0</v>
       </c>
@@ -10817,16 +10814,16 @@
       <c r="M40" s="5"/>
       <c r="N40" s="8"/>
       <c r="O40" s="47"/>
-      <c r="P40" s="262"/>
-      <c r="Q40" s="262"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="257"/>
+      <c r="D41" s="258"/>
+      <c r="E41" s="261"/>
+      <c r="F41" s="264"/>
       <c r="G41" s="23"/>
       <c r="H41" s="15"/>
       <c r="I41" s="2"/>
@@ -10836,16 +10833,16 @@
       <c r="M41" s="2"/>
       <c r="N41" s="9"/>
       <c r="O41" s="49"/>
-      <c r="P41" s="259"/>
-      <c r="Q41" s="259"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="251"/>
+      <c r="Q41" s="251"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="257"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="264"/>
       <c r="G42" s="23"/>
       <c r="H42" s="15"/>
       <c r="I42" s="2"/>
@@ -10855,16 +10852,16 @@
       <c r="M42" s="2"/>
       <c r="N42" s="9"/>
       <c r="O42" s="49"/>
-      <c r="P42" s="259"/>
-      <c r="Q42" s="259"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="251"/>
+      <c r="Q42" s="251"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="251"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="257"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="261"/>
+      <c r="F43" s="264"/>
       <c r="G43" s="20" t="s">
         <v>7</v>
       </c>
@@ -10876,16 +10873,16 @@
       <c r="M43" s="25"/>
       <c r="N43" s="26"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="259"/>
-      <c r="Q43" s="259"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="251"/>
+      <c r="Q43" s="251"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="251"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="257"/>
+      <c r="D44" s="258"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="264"/>
       <c r="G44" s="19"/>
       <c r="H44" s="15"/>
       <c r="I44" s="2"/>
@@ -10895,16 +10892,16 @@
       <c r="M44" s="2"/>
       <c r="N44" s="9"/>
       <c r="O44" s="49"/>
-      <c r="P44" s="259"/>
-      <c r="Q44" s="259"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="251"/>
+      <c r="Q44" s="251"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
-      <c r="D45" s="252"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="258"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="265"/>
       <c r="G45" s="19" t="s">
         <v>1</v>
       </c>
@@ -10916,16 +10913,16 @@
       <c r="M45" s="6"/>
       <c r="N45" s="10"/>
       <c r="O45" s="51"/>
-      <c r="P45" s="265"/>
-      <c r="Q45" s="265"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P45" s="252"/>
+      <c r="Q45" s="252"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="253"/>
-      <c r="F46" s="256"/>
+      <c r="D46" s="257"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="263"/>
       <c r="G46" s="22" t="s">
         <v>0</v>
       </c>
@@ -10937,16 +10934,16 @@
       <c r="M46" s="5"/>
       <c r="N46" s="8"/>
       <c r="O46" s="47"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="262"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P46" s="250"/>
+      <c r="Q46" s="250"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
-      <c r="D47" s="251"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="257"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="261"/>
+      <c r="F47" s="264"/>
       <c r="G47" s="23"/>
       <c r="H47" s="15"/>
       <c r="I47" s="2"/>
@@ -10956,16 +10953,16 @@
       <c r="M47" s="2"/>
       <c r="N47" s="9"/>
       <c r="O47" s="49"/>
-      <c r="P47" s="259"/>
-      <c r="Q47" s="259"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P47" s="251"/>
+      <c r="Q47" s="251"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
-      <c r="D48" s="251"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="257"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="261"/>
+      <c r="F48" s="264"/>
       <c r="G48" s="23"/>
       <c r="H48" s="15"/>
       <c r="I48" s="2"/>
@@ -10975,16 +10972,16 @@
       <c r="M48" s="2"/>
       <c r="N48" s="9"/>
       <c r="O48" s="49"/>
-      <c r="P48" s="259"/>
-      <c r="Q48" s="259"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P48" s="251"/>
+      <c r="Q48" s="251"/>
+    </row>
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="257"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="261"/>
+      <c r="F49" s="264"/>
       <c r="G49" s="20" t="s">
         <v>7</v>
       </c>
@@ -10996,16 +10993,16 @@
       <c r="M49" s="25"/>
       <c r="N49" s="26"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="259"/>
-      <c r="Q49" s="259"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P49" s="251"/>
+      <c r="Q49" s="251"/>
+    </row>
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="257"/>
+      <c r="D50" s="258"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="264"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
       <c r="I50" s="4"/>
@@ -11015,16 +11012,16 @@
       <c r="M50" s="4"/>
       <c r="N50" s="11"/>
       <c r="O50" s="52"/>
-      <c r="P50" s="259"/>
-      <c r="Q50" s="259"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50" s="251"/>
+      <c r="Q50" s="251"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
-      <c r="D51" s="252"/>
-      <c r="E51" s="255"/>
-      <c r="F51" s="258"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="265"/>
       <c r="G51" s="21" t="s">
         <v>1</v>
       </c>
@@ -11036,18 +11033,34 @@
       <c r="M51" s="6"/>
       <c r="N51" s="10"/>
       <c r="O51" s="51"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="265"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="Q40:Q45"/>
-    <mergeCell ref="Q46:Q51"/>
-    <mergeCell ref="Q4:Q9"/>
-    <mergeCell ref="Q16:Q21"/>
-    <mergeCell ref="Q22:Q27"/>
-    <mergeCell ref="Q28:Q33"/>
-    <mergeCell ref="Q34:Q39"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="P4:P9"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="P16:P21"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="P22:P27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="P28:P33"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="P34:P39"/>
     <mergeCell ref="D40:D45"/>
     <mergeCell ref="E40:E45"/>
     <mergeCell ref="F40:F45"/>
@@ -11056,29 +11069,13 @@
     <mergeCell ref="E46:E51"/>
     <mergeCell ref="F46:F51"/>
     <mergeCell ref="P46:P51"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="P34:P39"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="P16:P21"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="P22:P27"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="P4:P9"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="Q40:Q45"/>
+    <mergeCell ref="Q46:Q51"/>
+    <mergeCell ref="Q4:Q9"/>
+    <mergeCell ref="Q16:Q21"/>
+    <mergeCell ref="Q22:Q27"/>
+    <mergeCell ref="Q28:Q33"/>
+    <mergeCell ref="Q34:Q39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
